--- a/ws_test_file_use.xlsx
+++ b/ws_test_file_use.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuechen/PycharmProjects/LangGraph/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuechen/PycharmProjects/excel_agent_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B1B616-30CE-8D46-9BA4-5345B6DD51D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04BFE0B-2154-5A44-BEBD-9DF0CBA03C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1220" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="40960" windowHeight="20640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIGURATION" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="WL_asaibaijiang" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="102">
   <si>
     <t xml:space="preserve">SYSTEM MODULE </t>
   </si>
@@ -279,12 +279,158 @@
     <t>UBBMj10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Wireless Survey Report</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF Antenna
+Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. RF Antenna Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group 1 Wireless Antenna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antenna Height</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Azimuth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mechanical Tilt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electrical Tilt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency Band</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antenna Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group 2 Wireless Antenna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Additional Antenna1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Additional Antenna2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group 3 Wireless Antenna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group 4 Wireless Antenna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CMCC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2300M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1145M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2700M,3600M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100M,4900M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5300M,0350M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spcae Available for
+New RF Antenna(m)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF Free Pole(pcs)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. BBU &amp; DCDU Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -353,8 +499,36 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,6 +538,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,7 +1075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -941,29 +1133,200 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -971,15 +1334,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -995,166 +1349,55 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1577,112 +1820,112 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" ht="24" customHeight="1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="63"/>
-      <c r="W2" s="63"/>
-      <c r="X2" s="63"/>
-      <c r="Y2" s="63"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
     </row>
     <row r="3" spans="1:28" ht="15" thickBot="1"/>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="49" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24" t="s">
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="57" t="s">
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="24" t="s">
+      <c r="R4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="29" t="s">
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="W4" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="25" t="s">
+      <c r="X4" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26" t="s">
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AA4" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="31" t="s">
+      <c r="AB4" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="26" customHeight="1">
-      <c r="A5" s="46"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
       <c r="D5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="7" t="s">
         <v>10</v>
       </c>
@@ -1707,26 +1950,26 @@
       <c r="P5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="38" t="s">
+      <c r="Q5" s="67"/>
+      <c r="R5" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="S5" s="39"/>
-      <c r="T5" s="40" t="s">
+      <c r="S5" s="31"/>
+      <c r="T5" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="U5" s="41"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="43"/>
-      <c r="Z5" s="43"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="37"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="29"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="46"/>
-      <c r="B6" s="59" t="s">
+      <c r="A6" s="56"/>
+      <c r="B6" s="43" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="8">
@@ -1752,15 +1995,15 @@
       <c r="U6" s="18"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="20"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="54"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="14"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="46"/>
-      <c r="B7" s="60"/>
+      <c r="A7" s="56"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="8">
         <v>2</v>
       </c>
@@ -1784,15 +2027,15 @@
       <c r="U7" s="18"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="20"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="54"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="14"/>
     </row>
     <row r="8" spans="1:28">
-      <c r="A8" s="46"/>
-      <c r="B8" s="60"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="8">
         <v>3</v>
       </c>
@@ -1816,15 +2059,15 @@
       <c r="U8" s="18"/>
       <c r="V8" s="8"/>
       <c r="W8" s="8"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="20"/>
+      <c r="X8" s="53"/>
+      <c r="Y8" s="54"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="14"/>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="46"/>
-      <c r="B9" s="60"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="8">
         <v>4</v>
       </c>
@@ -1848,28 +2091,28 @@
       <c r="U9" s="18"/>
       <c r="V9" s="8"/>
       <c r="W9" s="8"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="20"/>
+      <c r="X9" s="53"/>
+      <c r="Y9" s="54"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="14"/>
     </row>
     <row r="10" spans="1:28">
-      <c r="A10" s="46"/>
-      <c r="B10" s="60"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="8">
         <v>1</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="48">
         <v>3</v>
       </c>
-      <c r="F10" s="56" t="s">
+      <c r="F10" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="56" t="s">
+      <c r="G10" s="51" t="s">
         <v>31</v>
       </c>
       <c r="H10" s="10">
@@ -1916,8 +2159,8 @@
       <c r="W10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="20"/>
+      <c r="X10" s="53"/>
+      <c r="Y10" s="54"/>
       <c r="Z10" s="8" t="s">
         <v>26</v>
       </c>
@@ -1927,13 +2170,13 @@
       <c r="AB10" s="14"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="46"/>
-      <c r="B11" s="60"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="8">
         <v>2</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="54"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="49"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="8">
@@ -1980,8 +2223,8 @@
       <c r="W11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="20"/>
+      <c r="X11" s="53"/>
+      <c r="Y11" s="54"/>
       <c r="Z11" s="8" t="s">
         <v>26</v>
       </c>
@@ -1991,13 +2234,13 @@
       <c r="AB11" s="14"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="46"/>
-      <c r="B12" s="60"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="54"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="49"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="8"/>
@@ -2016,22 +2259,22 @@
       <c r="U12" s="18"/>
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="20"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="54"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="15"/>
       <c r="AB12" s="14"/>
     </row>
     <row r="13" spans="1:28" ht="15" thickBot="1">
-      <c r="A13" s="47"/>
-      <c r="B13" s="61"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="12">
         <v>4</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
@@ -2042,96 +2285,96 @@
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="13"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="52"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="23"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="83"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="12"/>
       <c r="AB13" s="16"/>
     </row>
     <row r="14" spans="1:28" ht="15" thickBot="1"/>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="49" t="s">
+      <c r="E15" s="21"/>
+      <c r="F15" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="49" t="s">
+      <c r="G15" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="I15" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24" t="s">
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="57" t="s">
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="24" t="s">
+      <c r="R15" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="29" t="s">
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="W15" s="29" t="s">
+      <c r="W15" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="X15" s="25" t="s">
+      <c r="X15" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Y15" s="26"/>
-      <c r="Z15" s="26" t="s">
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="AA15" s="29" t="s">
+      <c r="AA15" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AB15" s="31" t="s">
+      <c r="AB15" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="26" customHeight="1">
-      <c r="A16" s="46"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
       <c r="I16" s="7" t="s">
         <v>10</v>
       </c>
@@ -2156,26 +2399,26 @@
       <c r="P16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="38" t="s">
+      <c r="Q16" s="67"/>
+      <c r="R16" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="S16" s="39"/>
-      <c r="T16" s="40" t="s">
+      <c r="S16" s="31"/>
+      <c r="T16" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="U16" s="41"/>
-      <c r="V16" s="44"/>
-      <c r="W16" s="44"/>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="44"/>
-      <c r="AB16" s="37"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="29"/>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="46"/>
-      <c r="B17" s="59" t="s">
+      <c r="A17" s="56"/>
+      <c r="B17" s="43" t="s">
         <v>58</v>
       </c>
       <c r="C17" s="8">
@@ -2237,8 +2480,8 @@
       <c r="W17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="20"/>
+      <c r="X17" s="53"/>
+      <c r="Y17" s="54"/>
       <c r="Z17" s="8" t="s">
         <v>22</v>
       </c>
@@ -2246,8 +2489,8 @@
       <c r="AB17" s="14"/>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="46"/>
-      <c r="B18" s="60"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="44"/>
       <c r="C18" s="8">
         <v>2</v>
       </c>
@@ -2299,8 +2542,8 @@
       <c r="W18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="20"/>
+      <c r="X18" s="53"/>
+      <c r="Y18" s="54"/>
       <c r="Z18" s="8" t="s">
         <v>22</v>
       </c>
@@ -2308,8 +2551,8 @@
       <c r="AB18" s="14"/>
     </row>
     <row r="19" spans="1:28">
-      <c r="A19" s="46"/>
-      <c r="B19" s="60"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="44"/>
       <c r="C19" s="8">
         <v>3</v>
       </c>
@@ -2333,15 +2576,15 @@
       <c r="U19" s="18"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="20"/>
+      <c r="X19" s="53"/>
+      <c r="Y19" s="54"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="14"/>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="46"/>
-      <c r="B20" s="60"/>
+      <c r="A20" s="56"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="8">
         <v>4</v>
       </c>
@@ -2365,28 +2608,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="20"/>
+      <c r="X20" s="53"/>
+      <c r="Y20" s="54"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="14"/>
     </row>
     <row r="21" spans="1:28" ht="14" customHeight="1">
-      <c r="A21" s="46"/>
-      <c r="B21" s="60"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="44"/>
       <c r="C21" s="8">
         <v>1</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="48">
         <v>3</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="G21" s="56" t="s">
+      <c r="G21" s="51" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="10">
@@ -2433,8 +2676,8 @@
       <c r="W21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="20"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="54"/>
       <c r="Z21" s="8" t="s">
         <v>26</v>
       </c>
@@ -2444,13 +2687,13 @@
       <c r="AB21" s="14"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="46"/>
-      <c r="B22" s="60"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="44"/>
       <c r="C22" s="8">
         <v>2</v>
       </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="54"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="49"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
       <c r="H22" s="8">
@@ -2497,8 +2740,8 @@
       <c r="W22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="20"/>
+      <c r="X22" s="53"/>
+      <c r="Y22" s="54"/>
       <c r="Z22" s="8" t="s">
         <v>26</v>
       </c>
@@ -2508,13 +2751,13 @@
       <c r="AB22" s="14"/>
     </row>
     <row r="23" spans="1:28">
-      <c r="A23" s="46"/>
-      <c r="B23" s="60"/>
+      <c r="A23" s="56"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="8">
         <v>3</v>
       </c>
-      <c r="D23" s="51"/>
-      <c r="E23" s="54"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="49"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="8"/>
@@ -2533,22 +2776,22 @@
       <c r="U23" s="18"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="20"/>
+      <c r="X23" s="53"/>
+      <c r="Y23" s="54"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="15"/>
       <c r="AB23" s="14"/>
     </row>
     <row r="24" spans="1:28" ht="15" thickBot="1">
-      <c r="A24" s="47"/>
-      <c r="B24" s="61"/>
+      <c r="A24" s="68"/>
+      <c r="B24" s="45"/>
       <c r="C24" s="12">
         <v>4</v>
       </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
@@ -2559,96 +2802,96 @@
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
       <c r="Q24" s="13"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
+      <c r="R24" s="52"/>
+      <c r="S24" s="52"/>
+      <c r="T24" s="52"/>
+      <c r="U24" s="52"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="23"/>
+      <c r="X24" s="82"/>
+      <c r="Y24" s="83"/>
       <c r="Z24" s="12"/>
       <c r="AA24" s="12"/>
       <c r="AB24" s="16"/>
     </row>
     <row r="25" spans="1:28" ht="15" thickBot="1"/>
     <row r="26" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A26" s="65" t="s">
+      <c r="A26" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="49" t="s">
+      <c r="E26" s="21"/>
+      <c r="F26" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="49" t="s">
+      <c r="G26" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="I26" s="24" t="s">
+      <c r="I26" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24" t="s">
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="57" t="s">
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="R26" s="24" t="s">
+      <c r="R26" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
-      <c r="U26" s="24"/>
-      <c r="V26" s="29" t="s">
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="W26" s="29" t="s">
+      <c r="W26" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="X26" s="25" t="s">
+      <c r="X26" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="26" t="s">
+      <c r="Y26" s="22"/>
+      <c r="Z26" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="AA26" s="29" t="s">
+      <c r="AA26" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AB26" s="31" t="s">
+      <c r="AB26" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="26" customHeight="1">
-      <c r="A27" s="66"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
+      <c r="A27" s="78"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
       <c r="D27" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
       <c r="I27" s="7" t="s">
         <v>10</v>
       </c>
@@ -2673,41 +2916,41 @@
       <c r="P27" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="Q27" s="64"/>
-      <c r="R27" s="33" t="s">
+      <c r="Q27" s="76"/>
+      <c r="R27" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S27" s="34"/>
-      <c r="T27" s="35" t="s">
+      <c r="S27" s="88"/>
+      <c r="T27" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="U27" s="36"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="32"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="63"/>
+      <c r="W27" s="63"/>
+      <c r="X27" s="84"/>
+      <c r="Y27" s="85"/>
+      <c r="Z27" s="85"/>
+      <c r="AA27" s="63"/>
+      <c r="AB27" s="86"/>
     </row>
     <row r="28" spans="1:28">
-      <c r="A28" s="66"/>
-      <c r="B28" s="59" t="s">
+      <c r="A28" s="78"/>
+      <c r="B28" s="43" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="8">
         <v>1</v>
       </c>
-      <c r="D28" s="59" t="s">
+      <c r="D28" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="68">
+      <c r="E28" s="70">
         <v>1</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="59" t="s">
+      <c r="G28" s="43" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="8">
@@ -2761,15 +3004,15 @@
       <c r="AB28" s="8"/>
     </row>
     <row r="29" spans="1:28">
-      <c r="A29" s="66"/>
-      <c r="B29" s="60"/>
+      <c r="A29" s="78"/>
+      <c r="B29" s="44"/>
       <c r="C29" s="8">
         <v>2</v>
       </c>
-      <c r="D29" s="60"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
       <c r="H29" s="8">
         <v>2</v>
       </c>
@@ -2821,15 +3064,15 @@
       <c r="AB29" s="8"/>
     </row>
     <row r="30" spans="1:28">
-      <c r="A30" s="66"/>
-      <c r="B30" s="60"/>
+      <c r="A30" s="78"/>
+      <c r="B30" s="44"/>
       <c r="C30" s="8">
         <v>3</v>
       </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
@@ -2853,15 +3096,15 @@
       <c r="AB30" s="8"/>
     </row>
     <row r="31" spans="1:28">
-      <c r="A31" s="66"/>
-      <c r="B31" s="60"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="44"/>
       <c r="C31" s="8">
         <v>4</v>
       </c>
-      <c r="D31" s="56"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="56"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="51"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
@@ -2885,19 +3128,19 @@
       <c r="AB31" s="8"/>
     </row>
     <row r="32" spans="1:28">
-      <c r="A32" s="66"/>
-      <c r="B32" s="60"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="44"/>
       <c r="C32" s="8">
         <v>1</v>
       </c>
-      <c r="D32" s="70" t="s">
+      <c r="D32" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="68">
+      <c r="E32" s="70">
         <v>3</v>
       </c>
-      <c r="F32" s="60"/>
-      <c r="G32" s="59" t="s">
+      <c r="F32" s="44"/>
+      <c r="G32" s="43" t="s">
         <v>34</v>
       </c>
       <c r="H32" s="8">
@@ -2953,15 +3196,15 @@
       <c r="AB32" s="8"/>
     </row>
     <row r="33" spans="1:28">
-      <c r="A33" s="66"/>
-      <c r="B33" s="60"/>
+      <c r="A33" s="78"/>
+      <c r="B33" s="44"/>
       <c r="C33" s="8">
         <v>2</v>
       </c>
-      <c r="D33" s="71"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
       <c r="H33" s="8">
         <v>3</v>
       </c>
@@ -3015,15 +3258,15 @@
       <c r="AB33" s="8"/>
     </row>
     <row r="34" spans="1:28">
-      <c r="A34" s="66"/>
-      <c r="B34" s="60"/>
+      <c r="A34" s="78"/>
+      <c r="B34" s="44"/>
       <c r="C34" s="8">
         <v>3</v>
       </c>
-      <c r="D34" s="71"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
@@ -3047,15 +3290,15 @@
       <c r="AB34" s="8"/>
     </row>
     <row r="35" spans="1:28">
-      <c r="A35" s="66"/>
-      <c r="B35" s="60"/>
+      <c r="A35" s="78"/>
+      <c r="B35" s="44"/>
       <c r="C35" s="8">
         <v>4</v>
       </c>
-      <c r="D35" s="71"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
@@ -3079,15 +3322,15 @@
       <c r="AB35" s="8"/>
     </row>
     <row r="36" spans="1:28">
-      <c r="A36" s="66"/>
-      <c r="B36" s="60"/>
+      <c r="A36" s="78"/>
+      <c r="B36" s="44"/>
       <c r="C36" s="8">
         <v>1</v>
       </c>
-      <c r="D36" s="71"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="60"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
       <c r="H36" s="8">
         <v>1</v>
       </c>
@@ -3141,15 +3384,15 @@
       <c r="AB36" s="8"/>
     </row>
     <row r="37" spans="1:28">
-      <c r="A37" s="66"/>
-      <c r="B37" s="60"/>
+      <c r="A37" s="78"/>
+      <c r="B37" s="44"/>
       <c r="C37" s="8">
         <v>2</v>
       </c>
-      <c r="D37" s="71"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
       <c r="H37" s="8">
         <v>1</v>
       </c>
@@ -3203,15 +3446,15 @@
       <c r="AB37" s="8"/>
     </row>
     <row r="38" spans="1:28">
-      <c r="A38" s="66"/>
-      <c r="B38" s="60"/>
+      <c r="A38" s="78"/>
+      <c r="B38" s="44"/>
       <c r="C38" s="8">
         <v>3</v>
       </c>
-      <c r="D38" s="71"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
@@ -3235,15 +3478,15 @@
       <c r="AB38" s="8"/>
     </row>
     <row r="39" spans="1:28" ht="15" thickBot="1">
-      <c r="A39" s="67"/>
-      <c r="B39" s="61"/>
+      <c r="A39" s="79"/>
+      <c r="B39" s="45"/>
       <c r="C39" s="12">
         <v>4</v>
       </c>
-      <c r="D39" s="72"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
@@ -3268,82 +3511,82 @@
     </row>
     <row r="40" spans="1:28" ht="15" thickBot="1"/>
     <row r="41" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A41" s="45" t="s">
+      <c r="A41" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="24"/>
-      <c r="F41" s="49" t="s">
+      <c r="E41" s="21"/>
+      <c r="F41" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="G41" s="49" t="s">
+      <c r="G41" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H41" s="49" t="s">
+      <c r="H41" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="I41" s="24" t="s">
+      <c r="I41" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24" t="s">
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="57" t="s">
+      <c r="M41" s="21"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="21"/>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="R41" s="24" t="s">
+      <c r="R41" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="S41" s="24"/>
-      <c r="T41" s="24"/>
-      <c r="U41" s="24"/>
-      <c r="V41" s="29" t="s">
+      <c r="S41" s="21"/>
+      <c r="T41" s="21"/>
+      <c r="U41" s="21"/>
+      <c r="V41" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="W41" s="29" t="s">
+      <c r="W41" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="X41" s="25" t="s">
+      <c r="X41" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Y41" s="26"/>
-      <c r="Z41" s="26" t="s">
+      <c r="Y41" s="22"/>
+      <c r="Z41" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="AA41" s="29" t="s">
+      <c r="AA41" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AB41" s="31" t="s">
+      <c r="AB41" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="26" customHeight="1">
-      <c r="A42" s="46"/>
-      <c r="B42" s="48"/>
-      <c r="C42" s="48"/>
+      <c r="A42" s="56"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
       <c r="D42" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="50"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
       <c r="I42" s="7" t="s">
         <v>10</v>
       </c>
@@ -3368,26 +3611,26 @@
       <c r="P42" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="58"/>
-      <c r="R42" s="38" t="s">
+      <c r="Q42" s="67"/>
+      <c r="R42" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="39"/>
-      <c r="T42" s="40" t="s">
+      <c r="S42" s="31"/>
+      <c r="T42" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="U42" s="41"/>
-      <c r="V42" s="44"/>
-      <c r="W42" s="44"/>
-      <c r="X42" s="42"/>
-      <c r="Y42" s="43"/>
-      <c r="Z42" s="43"/>
-      <c r="AA42" s="44"/>
-      <c r="AB42" s="37"/>
+      <c r="U42" s="33"/>
+      <c r="V42" s="25"/>
+      <c r="W42" s="25"/>
+      <c r="X42" s="27"/>
+      <c r="Y42" s="23"/>
+      <c r="Z42" s="23"/>
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="29"/>
     </row>
     <row r="43" spans="1:28">
-      <c r="A43" s="46"/>
-      <c r="B43" s="59" t="s">
+      <c r="A43" s="56"/>
+      <c r="B43" s="43" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="8">
@@ -3449,8 +3692,8 @@
       <c r="W43" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X43" s="19"/>
-      <c r="Y43" s="20"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="54"/>
       <c r="Z43" s="8" t="s">
         <v>26</v>
       </c>
@@ -3460,8 +3703,8 @@
       <c r="AB43" s="14"/>
     </row>
     <row r="44" spans="1:28">
-      <c r="A44" s="46"/>
-      <c r="B44" s="60"/>
+      <c r="A44" s="56"/>
+      <c r="B44" s="44"/>
       <c r="C44" s="8">
         <v>2</v>
       </c>
@@ -3513,8 +3756,8 @@
       <c r="W44" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X44" s="19"/>
-      <c r="Y44" s="20"/>
+      <c r="X44" s="53"/>
+      <c r="Y44" s="54"/>
       <c r="Z44" s="8" t="s">
         <v>26</v>
       </c>
@@ -3524,8 +3767,8 @@
       <c r="AB44" s="14"/>
     </row>
     <row r="45" spans="1:28">
-      <c r="A45" s="46"/>
-      <c r="B45" s="60"/>
+      <c r="A45" s="56"/>
+      <c r="B45" s="44"/>
       <c r="C45" s="8">
         <v>3</v>
       </c>
@@ -3549,15 +3792,15 @@
       <c r="U45" s="18"/>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
-      <c r="X45" s="19"/>
-      <c r="Y45" s="20"/>
+      <c r="X45" s="53"/>
+      <c r="Y45" s="54"/>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="14"/>
     </row>
     <row r="46" spans="1:28">
-      <c r="A46" s="46"/>
-      <c r="B46" s="60"/>
+      <c r="A46" s="56"/>
+      <c r="B46" s="44"/>
       <c r="C46" s="8">
         <v>4</v>
       </c>
@@ -3581,22 +3824,22 @@
       <c r="U46" s="18"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
-      <c r="X46" s="19"/>
-      <c r="Y46" s="20"/>
+      <c r="X46" s="53"/>
+      <c r="Y46" s="54"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="14"/>
     </row>
     <row r="47" spans="1:28">
-      <c r="A47" s="46"/>
-      <c r="B47" s="60"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="44"/>
       <c r="C47" s="8">
         <v>1</v>
       </c>
-      <c r="D47" s="51"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -3613,20 +3856,20 @@
       <c r="U47" s="18"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
-      <c r="X47" s="19"/>
-      <c r="Y47" s="20"/>
+      <c r="X47" s="53"/>
+      <c r="Y47" s="54"/>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="14"/>
     </row>
     <row r="48" spans="1:28">
-      <c r="A48" s="46"/>
-      <c r="B48" s="60"/>
+      <c r="A48" s="56"/>
+      <c r="B48" s="44"/>
       <c r="C48" s="8">
         <v>2</v>
       </c>
-      <c r="D48" s="51"/>
-      <c r="E48" s="54"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="49"/>
       <c r="F48" s="18"/>
       <c r="G48" s="18"/>
       <c r="H48" s="8"/>
@@ -3645,20 +3888,20 @@
       <c r="U48" s="18"/>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
-      <c r="X48" s="19"/>
-      <c r="Y48" s="20"/>
+      <c r="X48" s="53"/>
+      <c r="Y48" s="54"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="14"/>
     </row>
     <row r="49" spans="1:28">
-      <c r="A49" s="46"/>
-      <c r="B49" s="60"/>
+      <c r="A49" s="56"/>
+      <c r="B49" s="44"/>
       <c r="C49" s="8">
         <v>3</v>
       </c>
-      <c r="D49" s="51"/>
-      <c r="E49" s="54"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="49"/>
       <c r="F49" s="18"/>
       <c r="G49" s="18"/>
       <c r="H49" s="8"/>
@@ -3677,22 +3920,22 @@
       <c r="U49" s="18"/>
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
-      <c r="X49" s="19"/>
-      <c r="Y49" s="20"/>
+      <c r="X49" s="53"/>
+      <c r="Y49" s="54"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="15"/>
       <c r="AB49" s="14"/>
     </row>
     <row r="50" spans="1:28" ht="15" thickBot="1">
-      <c r="A50" s="47"/>
-      <c r="B50" s="61"/>
+      <c r="A50" s="68"/>
+      <c r="B50" s="45"/>
       <c r="C50" s="12">
         <v>4</v>
       </c>
-      <c r="D50" s="52"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
@@ -3703,14 +3946,14 @@
       <c r="O50" s="12"/>
       <c r="P50" s="12"/>
       <c r="Q50" s="13"/>
-      <c r="R50" s="21"/>
-      <c r="S50" s="21"/>
-      <c r="T50" s="21"/>
-      <c r="U50" s="21"/>
+      <c r="R50" s="52"/>
+      <c r="S50" s="52"/>
+      <c r="T50" s="52"/>
+      <c r="U50" s="52"/>
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
-      <c r="X50" s="22"/>
-      <c r="Y50" s="23"/>
+      <c r="X50" s="82"/>
+      <c r="Y50" s="83"/>
       <c r="Z50" s="12"/>
       <c r="AA50" s="12"/>
       <c r="AB50" s="16"/>
@@ -3718,210 +3961,210 @@
     <row r="51" spans="1:28" ht="15" thickBot="1"/>
     <row r="52" spans="1:28">
       <c r="A52" s="3"/>
-      <c r="C52" s="82" t="s">
+      <c r="C52" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="83"/>
-      <c r="Q52" s="83"/>
-      <c r="R52" s="83"/>
-      <c r="S52" s="83"/>
-      <c r="T52" s="83"/>
-      <c r="U52" s="83"/>
-      <c r="V52" s="83"/>
-      <c r="W52" s="83"/>
-      <c r="X52" s="84"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
+      <c r="S52" s="35"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="35"/>
+      <c r="V52" s="35"/>
+      <c r="W52" s="35"/>
+      <c r="X52" s="36"/>
       <c r="Y52" s="3"/>
     </row>
     <row r="53" spans="1:28">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="86"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="86"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
-      <c r="M53" s="86"/>
-      <c r="N53" s="86"/>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="86"/>
-      <c r="R53" s="86"/>
-      <c r="S53" s="86"/>
-      <c r="T53" s="86"/>
-      <c r="U53" s="86"/>
-      <c r="V53" s="86"/>
-      <c r="W53" s="86"/>
-      <c r="X53" s="87"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="38"/>
+      <c r="S53" s="38"/>
+      <c r="T53" s="38"/>
+      <c r="U53" s="38"/>
+      <c r="V53" s="38"/>
+      <c r="W53" s="38"/>
+      <c r="X53" s="39"/>
       <c r="Y53" s="3"/>
     </row>
     <row r="54" spans="1:28" ht="15" thickBot="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
-      <c r="C54" s="88"/>
-      <c r="D54" s="89"/>
-      <c r="E54" s="89"/>
-      <c r="F54" s="89"/>
-      <c r="G54" s="89"/>
-      <c r="H54" s="89"/>
-      <c r="I54" s="89"/>
-      <c r="J54" s="89"/>
-      <c r="K54" s="89"/>
-      <c r="L54" s="89"/>
-      <c r="M54" s="89"/>
-      <c r="N54" s="89"/>
-      <c r="O54" s="89"/>
-      <c r="P54" s="89"/>
-      <c r="Q54" s="89"/>
-      <c r="R54" s="89"/>
-      <c r="S54" s="89"/>
-      <c r="T54" s="89"/>
-      <c r="U54" s="89"/>
-      <c r="V54" s="89"/>
-      <c r="W54" s="89"/>
-      <c r="X54" s="90"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="41"/>
+      <c r="M54" s="41"/>
+      <c r="N54" s="41"/>
+      <c r="O54" s="41"/>
+      <c r="P54" s="41"/>
+      <c r="Q54" s="41"/>
+      <c r="R54" s="41"/>
+      <c r="S54" s="41"/>
+      <c r="T54" s="41"/>
+      <c r="U54" s="41"/>
+      <c r="V54" s="41"/>
+      <c r="W54" s="41"/>
+      <c r="X54" s="42"/>
       <c r="Y54" s="3"/>
     </row>
     <row r="55" spans="1:28" ht="15" thickBot="1"/>
     <row r="56" spans="1:28" ht="23" customHeight="1">
-      <c r="A56" s="45" t="s">
+      <c r="A56" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="B56" s="74" t="s">
+      <c r="B56" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="77"/>
-      <c r="F56" s="77"/>
-      <c r="G56" s="77"/>
-      <c r="H56" s="77"/>
-      <c r="I56" s="77"/>
-      <c r="J56" s="77"/>
-      <c r="K56" s="77"/>
-      <c r="L56" s="77"/>
-      <c r="M56" s="77"/>
-      <c r="N56" s="77"/>
-      <c r="O56" s="77"/>
-      <c r="P56" s="77"/>
-      <c r="Q56" s="77"/>
-      <c r="R56" s="77"/>
-      <c r="S56" s="77"/>
-      <c r="T56" s="77"/>
-      <c r="U56" s="77"/>
-      <c r="V56" s="77"/>
-      <c r="W56" s="77"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="60"/>
+      <c r="G56" s="60"/>
+      <c r="H56" s="60"/>
+      <c r="I56" s="60"/>
+      <c r="J56" s="60"/>
+      <c r="K56" s="60"/>
+      <c r="L56" s="60"/>
+      <c r="M56" s="60"/>
+      <c r="N56" s="60"/>
+      <c r="O56" s="60"/>
+      <c r="P56" s="60"/>
+      <c r="Q56" s="60"/>
+      <c r="R56" s="60"/>
+      <c r="S56" s="60"/>
+      <c r="T56" s="60"/>
+      <c r="U56" s="60"/>
+      <c r="V56" s="60"/>
+      <c r="W56" s="60"/>
       <c r="X56" s="4"/>
       <c r="Y56" s="5"/>
     </row>
     <row r="57" spans="1:28" ht="24" customHeight="1">
-      <c r="A57" s="46"/>
-      <c r="B57" s="75" t="s">
+      <c r="A57" s="56"/>
+      <c r="B57" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
-      <c r="I57" s="78"/>
-      <c r="J57" s="78"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="78"/>
-      <c r="M57" s="78"/>
-      <c r="N57" s="78"/>
-      <c r="O57" s="78"/>
-      <c r="P57" s="78"/>
-      <c r="Q57" s="78"/>
-      <c r="R57" s="78"/>
-      <c r="S57" s="78"/>
-      <c r="T57" s="78"/>
-      <c r="U57" s="78"/>
-      <c r="V57" s="78"/>
-      <c r="W57" s="78"/>
-      <c r="X57" s="78"/>
-      <c r="Y57" s="79"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="61"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
+      <c r="L57" s="61"/>
+      <c r="M57" s="61"/>
+      <c r="N57" s="61"/>
+      <c r="O57" s="61"/>
+      <c r="P57" s="61"/>
+      <c r="Q57" s="61"/>
+      <c r="R57" s="61"/>
+      <c r="S57" s="61"/>
+      <c r="T57" s="61"/>
+      <c r="U57" s="61"/>
+      <c r="V57" s="61"/>
+      <c r="W57" s="61"/>
+      <c r="X57" s="61"/>
+      <c r="Y57" s="62"/>
     </row>
     <row r="58" spans="1:28" ht="26" customHeight="1">
-      <c r="A58" s="46"/>
-      <c r="B58" s="75" t="s">
+      <c r="A58" s="56"/>
+      <c r="B58" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="75"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="78"/>
-      <c r="F58" s="78"/>
-      <c r="G58" s="78"/>
-      <c r="H58" s="78"/>
-      <c r="I58" s="78"/>
-      <c r="J58" s="78"/>
-      <c r="K58" s="78"/>
-      <c r="L58" s="78"/>
-      <c r="M58" s="78"/>
-      <c r="N58" s="78"/>
-      <c r="O58" s="78"/>
-      <c r="P58" s="78"/>
-      <c r="Q58" s="78"/>
-      <c r="R58" s="78"/>
-      <c r="S58" s="78"/>
-      <c r="T58" s="78"/>
-      <c r="U58" s="78"/>
-      <c r="V58" s="78"/>
-      <c r="W58" s="78"/>
-      <c r="X58" s="78"/>
-      <c r="Y58" s="79"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="61"/>
+      <c r="M58" s="61"/>
+      <c r="N58" s="61"/>
+      <c r="O58" s="61"/>
+      <c r="P58" s="61"/>
+      <c r="Q58" s="61"/>
+      <c r="R58" s="61"/>
+      <c r="S58" s="61"/>
+      <c r="T58" s="61"/>
+      <c r="U58" s="61"/>
+      <c r="V58" s="61"/>
+      <c r="W58" s="61"/>
+      <c r="X58" s="61"/>
+      <c r="Y58" s="62"/>
     </row>
     <row r="59" spans="1:28" ht="23" customHeight="1">
-      <c r="A59" s="46"/>
-      <c r="B59" s="75" t="s">
+      <c r="A59" s="56"/>
+      <c r="B59" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="75"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="78"/>
-      <c r="F59" s="78"/>
-      <c r="G59" s="78"/>
-      <c r="H59" s="78"/>
-      <c r="I59" s="78"/>
-      <c r="J59" s="78"/>
-      <c r="K59" s="78"/>
-      <c r="L59" s="78"/>
-      <c r="M59" s="78"/>
-      <c r="N59" s="78"/>
-      <c r="O59" s="78"/>
-      <c r="P59" s="78"/>
-      <c r="Q59" s="78"/>
-      <c r="R59" s="78"/>
-      <c r="S59" s="78"/>
-      <c r="T59" s="78"/>
-      <c r="U59" s="78"/>
-      <c r="V59" s="78"/>
-      <c r="W59" s="78"/>
-      <c r="X59" s="78"/>
-      <c r="Y59" s="79"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="61"/>
+      <c r="L59" s="61"/>
+      <c r="M59" s="61"/>
+      <c r="N59" s="61"/>
+      <c r="O59" s="61"/>
+      <c r="P59" s="61"/>
+      <c r="Q59" s="61"/>
+      <c r="R59" s="61"/>
+      <c r="S59" s="61"/>
+      <c r="T59" s="61"/>
+      <c r="U59" s="61"/>
+      <c r="V59" s="61"/>
+      <c r="W59" s="61"/>
+      <c r="X59" s="61"/>
+      <c r="Y59" s="62"/>
     </row>
     <row r="60" spans="1:28" ht="26" customHeight="1" thickBot="1">
-      <c r="A60" s="46"/>
-      <c r="B60" s="76"/>
-      <c r="C60" s="76"/>
-      <c r="D60" s="76"/>
+      <c r="A60" s="56"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -3945,35 +4188,234 @@
       <c r="Y60" s="2"/>
     </row>
     <row r="69" spans="2:25">
-      <c r="B69" s="80" t="s">
+      <c r="B69" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="81"/>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81"/>
-      <c r="H69" s="81"/>
-      <c r="I69" s="81"/>
-      <c r="J69" s="81"/>
-      <c r="K69" s="81"/>
-      <c r="L69" s="81"/>
-      <c r="M69" s="81"/>
-      <c r="N69" s="81"/>
-      <c r="O69" s="81"/>
-      <c r="P69" s="81"/>
-      <c r="Q69" s="81"/>
-      <c r="R69" s="81"/>
-      <c r="S69" s="81"/>
-      <c r="T69" s="81"/>
-      <c r="U69" s="81"/>
-      <c r="V69" s="81"/>
-      <c r="W69" s="81"/>
-      <c r="X69" s="81"/>
-      <c r="Y69" s="81"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="20"/>
+      <c r="L69" s="20"/>
+      <c r="M69" s="20"/>
+      <c r="N69" s="20"/>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20"/>
+      <c r="Q69" s="20"/>
+      <c r="R69" s="20"/>
+      <c r="S69" s="20"/>
+      <c r="T69" s="20"/>
+      <c r="U69" s="20"/>
+      <c r="V69" s="20"/>
+      <c r="W69" s="20"/>
+      <c r="X69" s="20"/>
+      <c r="Y69" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="223">
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="X37:Y37"/>
+    <mergeCell ref="X38:Y38"/>
+    <mergeCell ref="X39:Y39"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="X26:Y27"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AB26:AB27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="T47:U47"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="X48:Y48"/>
+    <mergeCell ref="X49:Y49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="AB41:AB42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="X43:Y43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="R41:U41"/>
+    <mergeCell ref="X41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="R26:U26"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="X15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="A15:A24"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:P4"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="A26:A39"/>
+    <mergeCell ref="B6:B13"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="D32:D39"/>
+    <mergeCell ref="E32:E39"/>
+    <mergeCell ref="F28:F39"/>
+    <mergeCell ref="G32:G39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L41:P41"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="T46:U46"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E56:W56"/>
+    <mergeCell ref="E57:Y57"/>
+    <mergeCell ref="E58:Y58"/>
+    <mergeCell ref="E59:Y59"/>
+    <mergeCell ref="V26:V27"/>
+    <mergeCell ref="W26:W27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:P26"/>
+    <mergeCell ref="G47:G50"/>
+    <mergeCell ref="V41:V42"/>
+    <mergeCell ref="W41:W42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
     <mergeCell ref="T10:U10"/>
     <mergeCell ref="T11:U11"/>
     <mergeCell ref="T12:U12"/>
@@ -3998,205 +4440,6 @@
     <mergeCell ref="F47:F50"/>
     <mergeCell ref="T13:U13"/>
     <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E56:W56"/>
-    <mergeCell ref="E57:Y57"/>
-    <mergeCell ref="E58:Y58"/>
-    <mergeCell ref="E59:Y59"/>
-    <mergeCell ref="V26:V27"/>
-    <mergeCell ref="W26:W27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:P26"/>
-    <mergeCell ref="G47:G50"/>
-    <mergeCell ref="V41:V42"/>
-    <mergeCell ref="W41:W42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L41:P41"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="A41:A50"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="G28:G31"/>
-    <mergeCell ref="D32:D39"/>
-    <mergeCell ref="E32:E39"/>
-    <mergeCell ref="F28:F39"/>
-    <mergeCell ref="G32:G39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A26:A39"/>
-    <mergeCell ref="B6:B13"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A4:A13"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:P4"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="A15:A24"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="AB15:AB16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="X15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="R41:U41"/>
-    <mergeCell ref="X41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="AB41:AB42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="X43:Y43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="T47:U47"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="X49:Y49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="X50:Y50"/>
-    <mergeCell ref="R26:U26"/>
-    <mergeCell ref="X26:Y27"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AB26:AB27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="X34:Y34"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="X37:Y37"/>
-    <mergeCell ref="X38:Y38"/>
-    <mergeCell ref="X39:Y39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="5">
@@ -4229,9 +4472,908 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="5" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.5" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="43.5" customHeight="1">
+      <c r="A1" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="61"/>
+      <c r="C3" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="96"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="98"/>
+      <c r="J4" s="99"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="100">
+        <v>77</v>
+      </c>
+      <c r="E5" s="100">
+        <v>77</v>
+      </c>
+      <c r="F5" s="100">
+        <v>77</v>
+      </c>
+      <c r="G5" s="100">
+        <v>77</v>
+      </c>
+      <c r="H5" s="100">
+        <v>77</v>
+      </c>
+      <c r="I5" s="101"/>
+      <c r="J5" s="99"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="100">
+        <v>78</v>
+      </c>
+      <c r="E6" s="100">
+        <v>118</v>
+      </c>
+      <c r="F6" s="100">
+        <v>227</v>
+      </c>
+      <c r="G6" s="100">
+        <v>78</v>
+      </c>
+      <c r="H6" s="100">
+        <v>78</v>
+      </c>
+      <c r="I6" s="101"/>
+      <c r="J6" s="99"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="61"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="100">
+        <v>4</v>
+      </c>
+      <c r="E7" s="100">
+        <v>4</v>
+      </c>
+      <c r="F7" s="100">
+        <v>0</v>
+      </c>
+      <c r="G7" s="100">
+        <v>4</v>
+      </c>
+      <c r="H7" s="100">
+        <v>4</v>
+      </c>
+      <c r="I7" s="101"/>
+      <c r="J7" s="99"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="61"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="101"/>
+      <c r="J8" s="99"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="61"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="97" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="101"/>
+      <c r="J9" s="99"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="61"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="103"/>
+      <c r="J10" s="99"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="93" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="99"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="97" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="98"/>
+      <c r="J12" s="99"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="61"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="100">
+        <v>67</v>
+      </c>
+      <c r="E13" s="100">
+        <v>67</v>
+      </c>
+      <c r="F13" s="100">
+        <v>67</v>
+      </c>
+      <c r="G13" s="100">
+        <v>77</v>
+      </c>
+      <c r="H13" s="100">
+        <v>77</v>
+      </c>
+      <c r="I13" s="101"/>
+      <c r="J13" s="99"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="100">
+        <v>23</v>
+      </c>
+      <c r="E14" s="100">
+        <v>73</v>
+      </c>
+      <c r="F14" s="100">
+        <v>289</v>
+      </c>
+      <c r="G14" s="100">
+        <v>77</v>
+      </c>
+      <c r="H14" s="100">
+        <v>79</v>
+      </c>
+      <c r="I14" s="101"/>
+      <c r="J14" s="99"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="100">
+        <v>0</v>
+      </c>
+      <c r="E15" s="100">
+        <v>4</v>
+      </c>
+      <c r="F15" s="100">
+        <v>9</v>
+      </c>
+      <c r="G15" s="100">
+        <v>2</v>
+      </c>
+      <c r="H15" s="100">
+        <v>4</v>
+      </c>
+      <c r="I15" s="101"/>
+      <c r="J15" s="99"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="61"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="100">
+        <v>2</v>
+      </c>
+      <c r="E16" s="100">
+        <v>4</v>
+      </c>
+      <c r="F16" s="100">
+        <v>6</v>
+      </c>
+      <c r="G16" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="101"/>
+      <c r="J16" s="99"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="61"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="97" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="100" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="100" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="100" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="101"/>
+      <c r="J17" s="99"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="61"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="102">
+        <v>11451479</v>
+      </c>
+      <c r="E18" s="102">
+        <v>11451479</v>
+      </c>
+      <c r="F18" s="102">
+        <v>11451479</v>
+      </c>
+      <c r="G18" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="103"/>
+      <c r="J18" s="99"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="93" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="99"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="61"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="97" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="61"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="100">
+        <v>56</v>
+      </c>
+      <c r="E21" s="100">
+        <v>56</v>
+      </c>
+      <c r="F21" s="100">
+        <v>57</v>
+      </c>
+      <c r="G21" s="100">
+        <v>58</v>
+      </c>
+      <c r="H21" s="100">
+        <v>56</v>
+      </c>
+      <c r="I21" s="101"/>
+      <c r="J21" s="99"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="100">
+        <v>40</v>
+      </c>
+      <c r="E22" s="100">
+        <v>20</v>
+      </c>
+      <c r="F22" s="100">
+        <v>60</v>
+      </c>
+      <c r="G22" s="100">
+        <v>22</v>
+      </c>
+      <c r="H22" s="100">
+        <v>19</v>
+      </c>
+      <c r="I22" s="101"/>
+      <c r="J22" s="99"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="61"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="100">
+        <v>8</v>
+      </c>
+      <c r="E23" s="100">
+        <v>0</v>
+      </c>
+      <c r="F23" s="100">
+        <v>0</v>
+      </c>
+      <c r="G23" s="100">
+        <v>0</v>
+      </c>
+      <c r="H23" s="100">
+        <v>2</v>
+      </c>
+      <c r="I23" s="101"/>
+      <c r="J23" s="99"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="61"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="I24" s="101"/>
+      <c r="J24" s="99"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="61"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="97" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="100" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="100" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="100" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="101"/>
+      <c r="J25" s="99"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="61"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="102">
+        <v>11451589</v>
+      </c>
+      <c r="E26" s="102">
+        <v>11451589</v>
+      </c>
+      <c r="F26" s="102">
+        <v>11451589</v>
+      </c>
+      <c r="G26" s="102">
+        <v>11451589</v>
+      </c>
+      <c r="H26" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="103"/>
+      <c r="J26" s="99"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="93" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="99"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="61"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="97" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="98"/>
+      <c r="J28" s="99"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="61"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="100">
+        <v>78</v>
+      </c>
+      <c r="H29" s="100">
+        <v>78</v>
+      </c>
+      <c r="I29" s="101"/>
+      <c r="J29" s="99"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="61"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="100"/>
+      <c r="G30" s="100">
+        <v>59</v>
+      </c>
+      <c r="H30" s="100">
+        <v>59</v>
+      </c>
+      <c r="I30" s="101"/>
+      <c r="J30" s="99"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100">
+        <v>8</v>
+      </c>
+      <c r="H31" s="100">
+        <v>8</v>
+      </c>
+      <c r="I31" s="101"/>
+      <c r="J31" s="99"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="61"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="I32" s="101"/>
+      <c r="J32" s="99"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="61"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="97" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" s="100" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" s="101"/>
+      <c r="J33" s="99"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="61"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="I34" s="103"/>
+      <c r="J34" s="99"/>
+    </row>
+    <row r="35" spans="1:10" ht="33.75" customHeight="1">
+      <c r="A35" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="107"/>
+      <c r="C35" s="97" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="101">
+        <v>32</v>
+      </c>
+      <c r="E35" s="101" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="101">
+        <v>22</v>
+      </c>
+      <c r="G35" s="101" t="s">
+        <v>96</v>
+      </c>
+      <c r="H35" s="101">
+        <v>22</v>
+      </c>
+      <c r="I35" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="101" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="34.75" customHeight="1">
+      <c r="A36" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="61"/>
+      <c r="C36" s="97" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="101">
+        <v>2</v>
+      </c>
+      <c r="E36" s="101" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="101">
+        <v>2</v>
+      </c>
+      <c r="G36" s="101" t="s">
+        <v>96</v>
+      </c>
+      <c r="H36" s="101">
+        <v>2</v>
+      </c>
+      <c r="I36" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="J36" s="101" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="93" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="94"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="94"/>
+      <c r="G37" s="94"/>
+      <c r="H37" s="94"/>
+      <c r="I37" s="94"/>
+      <c r="J37" s="94"/>
+    </row>
+    <row r="38" spans="1:10" ht="26" customHeight="1">
+      <c r="A38" s="101"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="101"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
+      <c r="F38" s="101"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+    </row>
+    <row r="39" spans="1:10" ht="37" customHeight="1">
+      <c r="A39" s="101"/>
+      <c r="B39" s="101"/>
+      <c r="C39" s="101"/>
+      <c r="D39" s="101"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="101"/>
+      <c r="B40" s="101"/>
+      <c r="C40" s="101"/>
+      <c r="D40" s="101"/>
+      <c r="E40" s="101"/>
+      <c r="F40" s="101"/>
+      <c r="G40" s="101"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="101"/>
+      <c r="B41" s="101"/>
+      <c r="C41" s="101"/>
+      <c r="D41" s="101"/>
+      <c r="E41" s="101"/>
+      <c r="F41" s="101"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="101"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="101"/>
+      <c r="D42" s="101"/>
+      <c r="E42" s="101"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="101"/>
+      <c r="B43" s="101"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="F42:J42"/>
+    <mergeCell ref="F43:J43"/>
+    <mergeCell ref="F44:J44"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B34"/>
+    <mergeCell ref="J4:J34"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C19:I19"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/ws_test_file_use.xlsx
+++ b/ws_test_file_use.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuechen/PycharmProjects/excel_agent_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04BFE0B-2154-5A44-BEBD-9DF0CBA03C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B80B99-465C-7344-BDA0-E4F5F876B0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="40960" windowHeight="20640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIGURATION" sheetId="1" r:id="rId1"/>
-    <sheet name="WL_asaibaijiang" sheetId="2" r:id="rId2"/>
+    <sheet name="WL_56A0DS6" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -1075,7 +1075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1130,7 +1130,241 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1139,45 +1373,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1190,9 +1385,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1203,201 +1395,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1820,112 +1817,112 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="76"/>
+      <c r="Y2" s="76"/>
     </row>
     <row r="3" spans="1:28" ht="15" thickBot="1"/>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="64" t="s">
+      <c r="E4" s="59"/>
+      <c r="F4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21" t="s">
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="66" t="s">
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="R4" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="24" t="s">
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="W4" s="24" t="s">
+      <c r="W4" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="26" t="s">
+      <c r="X4" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="Y4" s="22"/>
-      <c r="Z4" s="22" t="s">
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="24" t="s">
+      <c r="AA4" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="28" t="s">
+      <c r="AB4" s="45" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="26" customHeight="1">
-      <c r="A5" s="56"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
+      <c r="A5" s="64"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
       <c r="D5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
       <c r="I5" s="7" t="s">
         <v>10</v>
       </c>
@@ -1950,32 +1947,32 @@
       <c r="P5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="30" t="s">
+      <c r="Q5" s="78"/>
+      <c r="R5" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="S5" s="31"/>
-      <c r="T5" s="32" t="s">
+      <c r="S5" s="56"/>
+      <c r="T5" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="U5" s="33"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="29"/>
+      <c r="U5" s="58"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="60"/>
+      <c r="Y5" s="61"/>
+      <c r="Z5" s="61"/>
+      <c r="AA5" s="62"/>
+      <c r="AB5" s="54"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="56"/>
-      <c r="B6" s="43" t="s">
+      <c r="A6" s="64"/>
+      <c r="B6" s="82" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="8">
         <v>1</v>
       </c>
-      <c r="D6" s="18"/>
+      <c r="D6" s="38"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1989,25 +1986,25 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="9"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
-      <c r="X6" s="53"/>
-      <c r="Y6" s="54"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="37"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="14"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="56"/>
-      <c r="B7" s="44"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="83"/>
       <c r="C7" s="8">
         <v>2</v>
       </c>
-      <c r="D7" s="18"/>
+      <c r="D7" s="38"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -2021,25 +2018,25 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="9"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="54"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="37"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="14"/>
     </row>
     <row r="8" spans="1:28">
-      <c r="A8" s="56"/>
-      <c r="B8" s="44"/>
+      <c r="A8" s="64"/>
+      <c r="B8" s="83"/>
       <c r="C8" s="8">
         <v>3</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="38"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2053,25 +2050,25 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="9"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
       <c r="V8" s="8"/>
       <c r="W8" s="8"/>
-      <c r="X8" s="53"/>
-      <c r="Y8" s="54"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="37"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="14"/>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="56"/>
-      <c r="B9" s="44"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="83"/>
       <c r="C9" s="8">
         <v>4</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="38"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -2085,34 +2082,34 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="9"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
       <c r="V9" s="8"/>
       <c r="W9" s="8"/>
-      <c r="X9" s="53"/>
-      <c r="Y9" s="54"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="37"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="14"/>
     </row>
     <row r="10" spans="1:28">
-      <c r="A10" s="56"/>
-      <c r="B10" s="44"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="83"/>
       <c r="C10" s="8">
         <v>1</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="71">
         <v>3</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="51" t="s">
+      <c r="G10" s="74" t="s">
         <v>31</v>
       </c>
       <c r="H10" s="10">
@@ -2145,22 +2142,22 @@
       <c r="Q10" s="11">
         <v>50</v>
       </c>
-      <c r="R10" s="18">
+      <c r="R10" s="38">
         <v>0</v>
       </c>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18">
+      <c r="S10" s="38"/>
+      <c r="T10" s="38">
         <v>0</v>
       </c>
-      <c r="U10" s="18"/>
+      <c r="U10" s="38"/>
       <c r="V10" s="8">
         <v>5</v>
       </c>
       <c r="W10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="54"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="37"/>
       <c r="Z10" s="8" t="s">
         <v>26</v>
       </c>
@@ -2170,15 +2167,15 @@
       <c r="AB10" s="14"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="56"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="83"/>
       <c r="C11" s="8">
         <v>2</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="8">
         <v>3</v>
       </c>
@@ -2209,22 +2206,22 @@
       <c r="Q11" s="9">
         <v>130</v>
       </c>
-      <c r="R11" s="18">
+      <c r="R11" s="38">
         <v>0</v>
       </c>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18">
+      <c r="S11" s="38"/>
+      <c r="T11" s="38">
         <v>0</v>
       </c>
-      <c r="U11" s="18"/>
+      <c r="U11" s="38"/>
       <c r="V11" s="8">
         <v>5</v>
       </c>
       <c r="W11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X11" s="53"/>
-      <c r="Y11" s="54"/>
+      <c r="X11" s="36"/>
+      <c r="Y11" s="37"/>
       <c r="Z11" s="8" t="s">
         <v>26</v>
       </c>
@@ -2234,15 +2231,15 @@
       <c r="AB11" s="14"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="56"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="64"/>
+      <c r="B12" s="83"/>
       <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -2253,28 +2250,28 @@
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="9"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="54"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="37"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="15"/>
       <c r="AB12" s="14"/>
     </row>
     <row r="13" spans="1:28" ht="15" thickBot="1">
-      <c r="A13" s="68"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="12">
         <v>4</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
@@ -2285,96 +2282,96 @@
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="13"/>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="52"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="51"/>
+      <c r="U13" s="51"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
-      <c r="X13" s="82"/>
-      <c r="Y13" s="83"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="53"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="12"/>
       <c r="AB13" s="16"/>
     </row>
     <row r="14" spans="1:28" ht="15" thickBot="1"/>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="64" t="s">
+      <c r="E15" s="59"/>
+      <c r="F15" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="64" t="s">
+      <c r="H15" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21" t="s">
+      <c r="J15" s="59"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="66" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="59"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="21" t="s">
+      <c r="R15" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="24" t="s">
+      <c r="S15" s="59"/>
+      <c r="T15" s="59"/>
+      <c r="U15" s="59"/>
+      <c r="V15" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="W15" s="24" t="s">
+      <c r="W15" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="X15" s="26" t="s">
+      <c r="X15" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22" t="s">
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA15" s="24" t="s">
+      <c r="AA15" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="AB15" s="28" t="s">
+      <c r="AB15" s="45" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="26" customHeight="1">
-      <c r="A16" s="56"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
       <c r="I16" s="7" t="s">
         <v>10</v>
       </c>
@@ -2399,32 +2396,32 @@
       <c r="P16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="30" t="s">
+      <c r="Q16" s="78"/>
+      <c r="R16" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="S16" s="31"/>
-      <c r="T16" s="32" t="s">
+      <c r="S16" s="56"/>
+      <c r="T16" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="U16" s="33"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="29"/>
+      <c r="U16" s="58"/>
+      <c r="V16" s="62"/>
+      <c r="W16" s="62"/>
+      <c r="X16" s="60"/>
+      <c r="Y16" s="61"/>
+      <c r="Z16" s="61"/>
+      <c r="AA16" s="62"/>
+      <c r="AB16" s="54"/>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="56"/>
-      <c r="B17" s="43" t="s">
+      <c r="A17" s="64"/>
+      <c r="B17" s="82" t="s">
         <v>58</v>
       </c>
       <c r="C17" s="8">
         <v>1</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="38" t="s">
         <v>59</v>
       </c>
       <c r="E17" s="8">
@@ -2466,22 +2463,22 @@
       <c r="Q17" s="9">
         <v>50</v>
       </c>
-      <c r="R17" s="18">
+      <c r="R17" s="38">
         <v>0</v>
       </c>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18">
+      <c r="S17" s="38"/>
+      <c r="T17" s="38">
         <v>0</v>
       </c>
-      <c r="U17" s="18"/>
+      <c r="U17" s="38"/>
       <c r="V17" s="8">
         <v>5</v>
       </c>
       <c r="W17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X17" s="53"/>
-      <c r="Y17" s="54"/>
+      <c r="X17" s="36"/>
+      <c r="Y17" s="37"/>
       <c r="Z17" s="8" t="s">
         <v>22</v>
       </c>
@@ -2489,12 +2486,12 @@
       <c r="AB17" s="14"/>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="56"/>
-      <c r="B18" s="44"/>
+      <c r="A18" s="64"/>
+      <c r="B18" s="83"/>
       <c r="C18" s="8">
         <v>2</v>
       </c>
-      <c r="D18" s="18"/>
+      <c r="D18" s="38"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -2528,22 +2525,22 @@
       <c r="Q18" s="9">
         <v>50</v>
       </c>
-      <c r="R18" s="18">
+      <c r="R18" s="38">
         <v>0</v>
       </c>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18">
+      <c r="S18" s="38"/>
+      <c r="T18" s="38">
         <v>0</v>
       </c>
-      <c r="U18" s="18"/>
+      <c r="U18" s="38"/>
       <c r="V18" s="8">
         <v>5</v>
       </c>
       <c r="W18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X18" s="53"/>
-      <c r="Y18" s="54"/>
+      <c r="X18" s="36"/>
+      <c r="Y18" s="37"/>
       <c r="Z18" s="8" t="s">
         <v>22</v>
       </c>
@@ -2551,12 +2548,12 @@
       <c r="AB18" s="14"/>
     </row>
     <row r="19" spans="1:28">
-      <c r="A19" s="56"/>
-      <c r="B19" s="44"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="83"/>
       <c r="C19" s="8">
         <v>3</v>
       </c>
-      <c r="D19" s="18"/>
+      <c r="D19" s="38"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -2570,25 +2567,25 @@
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="9"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
-      <c r="X19" s="53"/>
-      <c r="Y19" s="54"/>
+      <c r="X19" s="36"/>
+      <c r="Y19" s="37"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="14"/>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="56"/>
-      <c r="B20" s="44"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="83"/>
       <c r="C20" s="8">
         <v>4</v>
       </c>
-      <c r="D20" s="18"/>
+      <c r="D20" s="38"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -2602,34 +2599,34 @@
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="9"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="54"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="37"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="14"/>
     </row>
     <row r="21" spans="1:28" ht="14" customHeight="1">
-      <c r="A21" s="56"/>
-      <c r="B21" s="44"/>
+      <c r="A21" s="64"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="8">
         <v>1</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="71">
         <v>3</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="G21" s="51" t="s">
+      <c r="G21" s="74" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="10">
@@ -2662,22 +2659,22 @@
       <c r="Q21" s="11">
         <v>50</v>
       </c>
-      <c r="R21" s="18">
+      <c r="R21" s="38">
         <v>0</v>
       </c>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18">
+      <c r="S21" s="38"/>
+      <c r="T21" s="38">
         <v>0</v>
       </c>
-      <c r="U21" s="18"/>
+      <c r="U21" s="38"/>
       <c r="V21" s="8">
         <v>5</v>
       </c>
       <c r="W21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="54"/>
+      <c r="X21" s="36"/>
+      <c r="Y21" s="37"/>
       <c r="Z21" s="8" t="s">
         <v>26</v>
       </c>
@@ -2687,15 +2684,15 @@
       <c r="AB21" s="14"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="56"/>
-      <c r="B22" s="44"/>
+      <c r="A22" s="64"/>
+      <c r="B22" s="83"/>
       <c r="C22" s="8">
         <v>2</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
       <c r="H22" s="8">
         <v>3</v>
       </c>
@@ -2726,22 +2723,22 @@
       <c r="Q22" s="9">
         <v>130</v>
       </c>
-      <c r="R22" s="18">
+      <c r="R22" s="38">
         <v>0</v>
       </c>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18">
+      <c r="S22" s="38"/>
+      <c r="T22" s="38">
         <v>0</v>
       </c>
-      <c r="U22" s="18"/>
+      <c r="U22" s="38"/>
       <c r="V22" s="8">
         <v>5</v>
       </c>
       <c r="W22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X22" s="53"/>
-      <c r="Y22" s="54"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="37"/>
       <c r="Z22" s="8" t="s">
         <v>26</v>
       </c>
@@ -2751,15 +2748,15 @@
       <c r="AB22" s="14"/>
     </row>
     <row r="23" spans="1:28">
-      <c r="A23" s="56"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="83"/>
       <c r="C23" s="8">
         <v>3</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
@@ -2770,28 +2767,28 @@
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="9"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
-      <c r="X23" s="53"/>
-      <c r="Y23" s="54"/>
+      <c r="X23" s="36"/>
+      <c r="Y23" s="37"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="15"/>
       <c r="AB23" s="14"/>
     </row>
     <row r="24" spans="1:28" ht="15" thickBot="1">
-      <c r="A24" s="68"/>
-      <c r="B24" s="45"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="84"/>
       <c r="C24" s="12">
         <v>4</v>
       </c>
-      <c r="D24" s="47"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
@@ -2802,96 +2799,96 @@
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
       <c r="Q24" s="13"/>
-      <c r="R24" s="52"/>
-      <c r="S24" s="52"/>
-      <c r="T24" s="52"/>
-      <c r="U24" s="52"/>
+      <c r="R24" s="51"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51"/>
+      <c r="U24" s="51"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
-      <c r="X24" s="82"/>
-      <c r="Y24" s="83"/>
+      <c r="X24" s="52"/>
+      <c r="Y24" s="53"/>
       <c r="Z24" s="12"/>
       <c r="AA24" s="12"/>
       <c r="AB24" s="16"/>
     </row>
     <row r="25" spans="1:28" ht="15" thickBot="1"/>
     <row r="26" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A26" s="77" t="s">
+      <c r="A26" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="64" t="s">
+      <c r="E26" s="59"/>
+      <c r="F26" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="64" t="s">
+      <c r="G26" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="64" t="s">
+      <c r="H26" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="I26" s="21" t="s">
+      <c r="I26" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21" t="s">
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="66" t="s">
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="R26" s="21" t="s">
+      <c r="R26" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="24" t="s">
+      <c r="S26" s="59"/>
+      <c r="T26" s="59"/>
+      <c r="U26" s="59"/>
+      <c r="V26" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="W26" s="24" t="s">
+      <c r="W26" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="X26" s="26" t="s">
+      <c r="X26" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="Y26" s="22"/>
-      <c r="Z26" s="22" t="s">
+      <c r="Y26" s="40"/>
+      <c r="Z26" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA26" s="24" t="s">
+      <c r="AA26" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="AB26" s="28" t="s">
+      <c r="AB26" s="45" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="26" customHeight="1">
-      <c r="A27" s="78"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
       <c r="I27" s="7" t="s">
         <v>10</v>
       </c>
@@ -2916,41 +2913,41 @@
       <c r="P27" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="Q27" s="76"/>
-      <c r="R27" s="87" t="s">
+      <c r="Q27" s="91"/>
+      <c r="R27" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="S27" s="88"/>
-      <c r="T27" s="89" t="s">
+      <c r="S27" s="48"/>
+      <c r="T27" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="U27" s="90"/>
-      <c r="V27" s="63"/>
-      <c r="W27" s="63"/>
-      <c r="X27" s="84"/>
-      <c r="Y27" s="85"/>
-      <c r="Z27" s="85"/>
-      <c r="AA27" s="63"/>
-      <c r="AB27" s="86"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="44"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="42"/>
+      <c r="Z27" s="42"/>
+      <c r="AA27" s="44"/>
+      <c r="AB27" s="46"/>
     </row>
     <row r="28" spans="1:28">
-      <c r="A28" s="78"/>
-      <c r="B28" s="43" t="s">
+      <c r="A28" s="80"/>
+      <c r="B28" s="82" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="8">
         <v>1</v>
       </c>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="70">
+      <c r="E28" s="85">
         <v>1</v>
       </c>
-      <c r="F28" s="43" t="s">
+      <c r="F28" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="43" t="s">
+      <c r="G28" s="82" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="8">
@@ -2983,20 +2980,20 @@
       <c r="Q28" s="8">
         <v>50</v>
       </c>
-      <c r="R28" s="18">
+      <c r="R28" s="38">
         <v>0</v>
       </c>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18">
+      <c r="S28" s="38"/>
+      <c r="T28" s="38">
         <v>0</v>
       </c>
-      <c r="U28" s="18"/>
+      <c r="U28" s="38"/>
       <c r="V28" s="8">
         <v>5</v>
       </c>
       <c r="W28" s="8"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="38"/>
       <c r="Z28" s="8" t="s">
         <v>22</v>
       </c>
@@ -3004,15 +3001,15 @@
       <c r="AB28" s="8"/>
     </row>
     <row r="29" spans="1:28">
-      <c r="A29" s="78"/>
-      <c r="B29" s="44"/>
+      <c r="A29" s="80"/>
+      <c r="B29" s="83"/>
       <c r="C29" s="8">
         <v>2</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
       <c r="H29" s="8">
         <v>2</v>
       </c>
@@ -3043,20 +3040,20 @@
       <c r="Q29" s="8">
         <v>50</v>
       </c>
-      <c r="R29" s="18">
+      <c r="R29" s="38">
         <v>0</v>
       </c>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18">
+      <c r="S29" s="38"/>
+      <c r="T29" s="38">
         <v>0</v>
       </c>
-      <c r="U29" s="18"/>
+      <c r="U29" s="38"/>
       <c r="V29" s="8">
         <v>5</v>
       </c>
       <c r="W29" s="8"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="38"/>
       <c r="Z29" s="8" t="s">
         <v>22</v>
       </c>
@@ -3064,15 +3061,15 @@
       <c r="AB29" s="8"/>
     </row>
     <row r="30" spans="1:28">
-      <c r="A30" s="78"/>
-      <c r="B30" s="44"/>
+      <c r="A30" s="80"/>
+      <c r="B30" s="83"/>
       <c r="C30" s="8">
         <v>3</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
@@ -3083,28 +3080,28 @@
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="38"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="38"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
+      <c r="X30" s="38"/>
+      <c r="Y30" s="38"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
     </row>
     <row r="31" spans="1:28">
-      <c r="A31" s="78"/>
-      <c r="B31" s="44"/>
+      <c r="A31" s="80"/>
+      <c r="B31" s="83"/>
       <c r="C31" s="8">
         <v>4</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="51"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="74"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
@@ -3115,32 +3112,32 @@
       <c r="O31" s="8"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
     </row>
     <row r="32" spans="1:28">
-      <c r="A32" s="78"/>
-      <c r="B32" s="44"/>
+      <c r="A32" s="80"/>
+      <c r="B32" s="83"/>
       <c r="C32" s="8">
         <v>1</v>
       </c>
-      <c r="D32" s="72" t="s">
+      <c r="D32" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="70">
+      <c r="E32" s="85">
         <v>3</v>
       </c>
-      <c r="F32" s="44"/>
-      <c r="G32" s="43" t="s">
+      <c r="F32" s="83"/>
+      <c r="G32" s="82" t="s">
         <v>34</v>
       </c>
       <c r="H32" s="8">
@@ -3173,20 +3170,20 @@
       <c r="Q32" s="8">
         <v>50</v>
       </c>
-      <c r="R32" s="18">
+      <c r="R32" s="38">
         <v>0</v>
       </c>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18">
+      <c r="S32" s="38"/>
+      <c r="T32" s="38">
         <v>0</v>
       </c>
-      <c r="U32" s="18"/>
+      <c r="U32" s="38"/>
       <c r="V32" s="8">
         <v>5</v>
       </c>
       <c r="W32" s="8"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
       <c r="Z32" s="8" t="s">
         <v>26</v>
       </c>
@@ -3196,15 +3193,15 @@
       <c r="AB32" s="8"/>
     </row>
     <row r="33" spans="1:28">
-      <c r="A33" s="78"/>
-      <c r="B33" s="44"/>
+      <c r="A33" s="80"/>
+      <c r="B33" s="83"/>
       <c r="C33" s="8">
         <v>2</v>
       </c>
-      <c r="D33" s="73"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
       <c r="H33" s="8">
         <v>3</v>
       </c>
@@ -3235,20 +3232,20 @@
       <c r="Q33" s="8">
         <v>130</v>
       </c>
-      <c r="R33" s="18">
+      <c r="R33" s="38">
         <v>0</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18">
+      <c r="S33" s="38"/>
+      <c r="T33" s="38">
         <v>0</v>
       </c>
-      <c r="U33" s="18"/>
+      <c r="U33" s="38"/>
       <c r="V33" s="8">
         <v>5</v>
       </c>
       <c r="W33" s="8"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
+      <c r="X33" s="38"/>
+      <c r="Y33" s="38"/>
       <c r="Z33" s="8" t="s">
         <v>26</v>
       </c>
@@ -3258,15 +3255,15 @@
       <c r="AB33" s="8"/>
     </row>
     <row r="34" spans="1:28">
-      <c r="A34" s="78"/>
-      <c r="B34" s="44"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="83"/>
       <c r="C34" s="8">
         <v>3</v>
       </c>
-      <c r="D34" s="73"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
@@ -3277,28 +3274,28 @@
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
+      <c r="X34" s="38"/>
+      <c r="Y34" s="38"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
     </row>
     <row r="35" spans="1:28">
-      <c r="A35" s="78"/>
-      <c r="B35" s="44"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="83"/>
       <c r="C35" s="8">
         <v>4</v>
       </c>
-      <c r="D35" s="73"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
@@ -3309,28 +3306,28 @@
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="38"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
+      <c r="X35" s="38"/>
+      <c r="Y35" s="38"/>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
     </row>
     <row r="36" spans="1:28">
-      <c r="A36" s="78"/>
-      <c r="B36" s="44"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="83"/>
       <c r="C36" s="8">
         <v>1</v>
       </c>
-      <c r="D36" s="73"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
+      <c r="D36" s="88"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
       <c r="H36" s="8">
         <v>1</v>
       </c>
@@ -3361,20 +3358,20 @@
       <c r="Q36" s="8">
         <v>50</v>
       </c>
-      <c r="R36" s="18">
+      <c r="R36" s="38">
         <v>0</v>
       </c>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18">
+      <c r="S36" s="38"/>
+      <c r="T36" s="38">
         <v>0</v>
       </c>
-      <c r="U36" s="18"/>
+      <c r="U36" s="38"/>
       <c r="V36" s="8">
         <v>5</v>
       </c>
       <c r="W36" s="8"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
       <c r="Z36" s="8" t="s">
         <v>26</v>
       </c>
@@ -3384,15 +3381,15 @@
       <c r="AB36" s="8"/>
     </row>
     <row r="37" spans="1:28">
-      <c r="A37" s="78"/>
-      <c r="B37" s="44"/>
+      <c r="A37" s="80"/>
+      <c r="B37" s="83"/>
       <c r="C37" s="8">
         <v>2</v>
       </c>
-      <c r="D37" s="73"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
       <c r="H37" s="8">
         <v>1</v>
       </c>
@@ -3423,20 +3420,20 @@
       <c r="Q37" s="8">
         <v>130</v>
       </c>
-      <c r="R37" s="18">
+      <c r="R37" s="38">
         <v>0</v>
       </c>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18">
+      <c r="S37" s="38"/>
+      <c r="T37" s="38">
         <v>0</v>
       </c>
-      <c r="U37" s="18"/>
+      <c r="U37" s="38"/>
       <c r="V37" s="8">
         <v>5</v>
       </c>
       <c r="W37" s="8"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
+      <c r="X37" s="38"/>
+      <c r="Y37" s="38"/>
       <c r="Z37" s="8" t="s">
         <v>26</v>
       </c>
@@ -3446,15 +3443,15 @@
       <c r="AB37" s="8"/>
     </row>
     <row r="38" spans="1:28">
-      <c r="A38" s="78"/>
-      <c r="B38" s="44"/>
+      <c r="A38" s="80"/>
+      <c r="B38" s="83"/>
       <c r="C38" s="8">
         <v>3</v>
       </c>
-      <c r="D38" s="73"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
+      <c r="D38" s="88"/>
+      <c r="E38" s="86"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
@@ -3465,28 +3462,28 @@
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
     </row>
     <row r="39" spans="1:28" ht="15" thickBot="1">
-      <c r="A39" s="79"/>
-      <c r="B39" s="45"/>
+      <c r="A39" s="81"/>
+      <c r="B39" s="84"/>
       <c r="C39" s="12">
         <v>4</v>
       </c>
-      <c r="D39" s="74"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
@@ -3497,96 +3494,96 @@
       <c r="O39" s="12"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="38"/>
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
+      <c r="X39" s="38"/>
+      <c r="Y39" s="38"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
     </row>
     <row r="40" spans="1:28" ht="15" thickBot="1"/>
     <row r="41" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A41" s="55" t="s">
+      <c r="A41" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="21"/>
-      <c r="F41" s="64" t="s">
+      <c r="E41" s="59"/>
+      <c r="F41" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="H41" s="64" t="s">
+      <c r="H41" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="I41" s="21" t="s">
+      <c r="I41" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21" t="s">
+      <c r="J41" s="59"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M41" s="21"/>
-      <c r="N41" s="21"/>
-      <c r="O41" s="21"/>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="66" t="s">
+      <c r="M41" s="59"/>
+      <c r="N41" s="59"/>
+      <c r="O41" s="59"/>
+      <c r="P41" s="59"/>
+      <c r="Q41" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="R41" s="21" t="s">
+      <c r="R41" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="S41" s="21"/>
-      <c r="T41" s="21"/>
-      <c r="U41" s="21"/>
-      <c r="V41" s="24" t="s">
+      <c r="S41" s="59"/>
+      <c r="T41" s="59"/>
+      <c r="U41" s="59"/>
+      <c r="V41" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="W41" s="24" t="s">
+      <c r="W41" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="X41" s="26" t="s">
+      <c r="X41" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="Y41" s="22"/>
-      <c r="Z41" s="22" t="s">
+      <c r="Y41" s="40"/>
+      <c r="Z41" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA41" s="24" t="s">
+      <c r="AA41" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="AB41" s="28" t="s">
+      <c r="AB41" s="45" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="26" customHeight="1">
-      <c r="A42" s="56"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
       <c r="D42" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="68"/>
       <c r="I42" s="7" t="s">
         <v>10</v>
       </c>
@@ -3611,32 +3608,32 @@
       <c r="P42" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="67"/>
-      <c r="R42" s="30" t="s">
+      <c r="Q42" s="78"/>
+      <c r="R42" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="31"/>
-      <c r="T42" s="32" t="s">
+      <c r="S42" s="56"/>
+      <c r="T42" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="U42" s="33"/>
-      <c r="V42" s="25"/>
-      <c r="W42" s="25"/>
-      <c r="X42" s="27"/>
-      <c r="Y42" s="23"/>
-      <c r="Z42" s="23"/>
-      <c r="AA42" s="25"/>
-      <c r="AB42" s="29"/>
+      <c r="U42" s="58"/>
+      <c r="V42" s="62"/>
+      <c r="W42" s="62"/>
+      <c r="X42" s="60"/>
+      <c r="Y42" s="61"/>
+      <c r="Z42" s="61"/>
+      <c r="AA42" s="62"/>
+      <c r="AB42" s="54"/>
     </row>
     <row r="43" spans="1:28">
-      <c r="A43" s="56"/>
-      <c r="B43" s="43" t="s">
+      <c r="A43" s="64"/>
+      <c r="B43" s="82" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="8">
         <v>1</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="38" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="8">
@@ -3678,22 +3675,22 @@
       <c r="Q43" s="9">
         <v>50</v>
       </c>
-      <c r="R43" s="18">
+      <c r="R43" s="38">
         <v>0</v>
       </c>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18">
+      <c r="S43" s="38"/>
+      <c r="T43" s="38">
         <v>0</v>
       </c>
-      <c r="U43" s="18"/>
+      <c r="U43" s="38"/>
       <c r="V43" s="8">
         <v>5</v>
       </c>
       <c r="W43" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="54"/>
+      <c r="X43" s="36"/>
+      <c r="Y43" s="37"/>
       <c r="Z43" s="8" t="s">
         <v>26</v>
       </c>
@@ -3703,12 +3700,12 @@
       <c r="AB43" s="14"/>
     </row>
     <row r="44" spans="1:28">
-      <c r="A44" s="56"/>
-      <c r="B44" s="44"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="83"/>
       <c r="C44" s="8">
         <v>2</v>
       </c>
-      <c r="D44" s="18"/>
+      <c r="D44" s="38"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
@@ -3742,22 +3739,22 @@
       <c r="Q44" s="9">
         <v>130</v>
       </c>
-      <c r="R44" s="18">
+      <c r="R44" s="38">
         <v>0</v>
       </c>
-      <c r="S44" s="18"/>
-      <c r="T44" s="18">
+      <c r="S44" s="38"/>
+      <c r="T44" s="38">
         <v>0</v>
       </c>
-      <c r="U44" s="18"/>
+      <c r="U44" s="38"/>
       <c r="V44" s="8">
         <v>5</v>
       </c>
       <c r="W44" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X44" s="53"/>
-      <c r="Y44" s="54"/>
+      <c r="X44" s="36"/>
+      <c r="Y44" s="37"/>
       <c r="Z44" s="8" t="s">
         <v>26</v>
       </c>
@@ -3767,12 +3764,12 @@
       <c r="AB44" s="14"/>
     </row>
     <row r="45" spans="1:28">
-      <c r="A45" s="56"/>
-      <c r="B45" s="44"/>
+      <c r="A45" s="64"/>
+      <c r="B45" s="83"/>
       <c r="C45" s="8">
         <v>3</v>
       </c>
-      <c r="D45" s="18"/>
+      <c r="D45" s="38"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
@@ -3786,25 +3783,25 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
+      <c r="R45" s="38"/>
+      <c r="S45" s="38"/>
+      <c r="T45" s="38"/>
+      <c r="U45" s="38"/>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
-      <c r="X45" s="53"/>
-      <c r="Y45" s="54"/>
+      <c r="X45" s="36"/>
+      <c r="Y45" s="37"/>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="14"/>
     </row>
     <row r="46" spans="1:28">
-      <c r="A46" s="56"/>
-      <c r="B46" s="44"/>
+      <c r="A46" s="64"/>
+      <c r="B46" s="83"/>
       <c r="C46" s="8">
         <v>4</v>
       </c>
-      <c r="D46" s="18"/>
+      <c r="D46" s="38"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
@@ -3818,28 +3815,28 @@
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
       <c r="Q46" s="9"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
+      <c r="R46" s="38"/>
+      <c r="S46" s="38"/>
+      <c r="T46" s="38"/>
+      <c r="U46" s="38"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
-      <c r="X46" s="53"/>
-      <c r="Y46" s="54"/>
+      <c r="X46" s="36"/>
+      <c r="Y46" s="37"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="14"/>
     </row>
     <row r="47" spans="1:28">
-      <c r="A47" s="56"/>
-      <c r="B47" s="44"/>
+      <c r="A47" s="64"/>
+      <c r="B47" s="83"/>
       <c r="C47" s="8">
         <v>1</v>
       </c>
-      <c r="D47" s="46"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="51"/>
-      <c r="G47" s="51"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -3850,28 +3847,28 @@
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
       <c r="Q47" s="11"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
+      <c r="R47" s="38"/>
+      <c r="S47" s="38"/>
+      <c r="T47" s="38"/>
+      <c r="U47" s="38"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
-      <c r="X47" s="53"/>
-      <c r="Y47" s="54"/>
+      <c r="X47" s="36"/>
+      <c r="Y47" s="37"/>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="14"/>
     </row>
     <row r="48" spans="1:28">
-      <c r="A48" s="56"/>
-      <c r="B48" s="44"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="83"/>
       <c r="C48" s="8">
         <v>2</v>
       </c>
-      <c r="D48" s="46"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="38"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
@@ -3882,28 +3879,28 @@
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
       <c r="Q48" s="9"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
+      <c r="R48" s="38"/>
+      <c r="S48" s="38"/>
+      <c r="T48" s="38"/>
+      <c r="U48" s="38"/>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
-      <c r="X48" s="53"/>
-      <c r="Y48" s="54"/>
+      <c r="X48" s="36"/>
+      <c r="Y48" s="37"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="14"/>
     </row>
     <row r="49" spans="1:28">
-      <c r="A49" s="56"/>
-      <c r="B49" s="44"/>
+      <c r="A49" s="64"/>
+      <c r="B49" s="83"/>
       <c r="C49" s="8">
         <v>3</v>
       </c>
-      <c r="D49" s="46"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -3914,28 +3911,28 @@
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
       <c r="Q49" s="9"/>
-      <c r="R49" s="18"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="18"/>
-      <c r="U49" s="18"/>
+      <c r="R49" s="38"/>
+      <c r="S49" s="38"/>
+      <c r="T49" s="38"/>
+      <c r="U49" s="38"/>
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
-      <c r="X49" s="53"/>
-      <c r="Y49" s="54"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="37"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="15"/>
       <c r="AB49" s="14"/>
     </row>
     <row r="50" spans="1:28" ht="15" thickBot="1">
-      <c r="A50" s="68"/>
-      <c r="B50" s="45"/>
+      <c r="A50" s="65"/>
+      <c r="B50" s="84"/>
       <c r="C50" s="12">
         <v>4</v>
       </c>
-      <c r="D50" s="47"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
@@ -3946,14 +3943,14 @@
       <c r="O50" s="12"/>
       <c r="P50" s="12"/>
       <c r="Q50" s="13"/>
-      <c r="R50" s="52"/>
-      <c r="S50" s="52"/>
-      <c r="T50" s="52"/>
-      <c r="U50" s="52"/>
+      <c r="R50" s="51"/>
+      <c r="S50" s="51"/>
+      <c r="T50" s="51"/>
+      <c r="U50" s="51"/>
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
-      <c r="X50" s="82"/>
-      <c r="Y50" s="83"/>
+      <c r="X50" s="52"/>
+      <c r="Y50" s="53"/>
       <c r="Z50" s="12"/>
       <c r="AA50" s="12"/>
       <c r="AB50" s="16"/>
@@ -3961,210 +3958,210 @@
     <row r="51" spans="1:28" ht="15" thickBot="1"/>
     <row r="52" spans="1:28">
       <c r="A52" s="3"/>
-      <c r="C52" s="34" t="s">
+      <c r="C52" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
-      <c r="L52" s="35"/>
-      <c r="M52" s="35"/>
-      <c r="N52" s="35"/>
-      <c r="O52" s="35"/>
-      <c r="P52" s="35"/>
-      <c r="Q52" s="35"/>
-      <c r="R52" s="35"/>
-      <c r="S52" s="35"/>
-      <c r="T52" s="35"/>
-      <c r="U52" s="35"/>
-      <c r="V52" s="35"/>
-      <c r="W52" s="35"/>
-      <c r="X52" s="36"/>
+      <c r="D52" s="100"/>
+      <c r="E52" s="100"/>
+      <c r="F52" s="100"/>
+      <c r="G52" s="100"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="100"/>
+      <c r="J52" s="100"/>
+      <c r="K52" s="100"/>
+      <c r="L52" s="100"/>
+      <c r="M52" s="100"/>
+      <c r="N52" s="100"/>
+      <c r="O52" s="100"/>
+      <c r="P52" s="100"/>
+      <c r="Q52" s="100"/>
+      <c r="R52" s="100"/>
+      <c r="S52" s="100"/>
+      <c r="T52" s="100"/>
+      <c r="U52" s="100"/>
+      <c r="V52" s="100"/>
+      <c r="W52" s="100"/>
+      <c r="X52" s="101"/>
       <c r="Y52" s="3"/>
     </row>
     <row r="53" spans="1:28">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="38"/>
-      <c r="N53" s="38"/>
-      <c r="O53" s="38"/>
-      <c r="P53" s="38"/>
-      <c r="Q53" s="38"/>
-      <c r="R53" s="38"/>
-      <c r="S53" s="38"/>
-      <c r="T53" s="38"/>
-      <c r="U53" s="38"/>
-      <c r="V53" s="38"/>
-      <c r="W53" s="38"/>
-      <c r="X53" s="39"/>
+      <c r="C53" s="102"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="27"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27"/>
+      <c r="O53" s="27"/>
+      <c r="P53" s="27"/>
+      <c r="Q53" s="27"/>
+      <c r="R53" s="27"/>
+      <c r="S53" s="27"/>
+      <c r="T53" s="27"/>
+      <c r="U53" s="27"/>
+      <c r="V53" s="27"/>
+      <c r="W53" s="27"/>
+      <c r="X53" s="103"/>
       <c r="Y53" s="3"/>
     </row>
     <row r="54" spans="1:28" ht="15" thickBot="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
-      <c r="N54" s="41"/>
-      <c r="O54" s="41"/>
-      <c r="P54" s="41"/>
-      <c r="Q54" s="41"/>
-      <c r="R54" s="41"/>
-      <c r="S54" s="41"/>
-      <c r="T54" s="41"/>
-      <c r="U54" s="41"/>
-      <c r="V54" s="41"/>
-      <c r="W54" s="41"/>
-      <c r="X54" s="42"/>
+      <c r="C54" s="104"/>
+      <c r="D54" s="105"/>
+      <c r="E54" s="105"/>
+      <c r="F54" s="105"/>
+      <c r="G54" s="105"/>
+      <c r="H54" s="105"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="105"/>
+      <c r="K54" s="105"/>
+      <c r="L54" s="105"/>
+      <c r="M54" s="105"/>
+      <c r="N54" s="105"/>
+      <c r="O54" s="105"/>
+      <c r="P54" s="105"/>
+      <c r="Q54" s="105"/>
+      <c r="R54" s="105"/>
+      <c r="S54" s="105"/>
+      <c r="T54" s="105"/>
+      <c r="U54" s="105"/>
+      <c r="V54" s="105"/>
+      <c r="W54" s="105"/>
+      <c r="X54" s="106"/>
       <c r="Y54" s="3"/>
     </row>
     <row r="55" spans="1:28" ht="15" thickBot="1"/>
     <row r="56" spans="1:28" ht="23" customHeight="1">
-      <c r="A56" s="55" t="s">
+      <c r="A56" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="57"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="60"/>
-      <c r="G56" s="60"/>
-      <c r="H56" s="60"/>
-      <c r="I56" s="60"/>
-      <c r="J56" s="60"/>
-      <c r="K56" s="60"/>
-      <c r="L56" s="60"/>
-      <c r="M56" s="60"/>
-      <c r="N56" s="60"/>
-      <c r="O56" s="60"/>
-      <c r="P56" s="60"/>
-      <c r="Q56" s="60"/>
-      <c r="R56" s="60"/>
-      <c r="S56" s="60"/>
-      <c r="T56" s="60"/>
-      <c r="U56" s="60"/>
-      <c r="V56" s="60"/>
-      <c r="W56" s="60"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
+      <c r="E56" s="95"/>
+      <c r="F56" s="95"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="95"/>
+      <c r="I56" s="95"/>
+      <c r="J56" s="95"/>
+      <c r="K56" s="95"/>
+      <c r="L56" s="95"/>
+      <c r="M56" s="95"/>
+      <c r="N56" s="95"/>
+      <c r="O56" s="95"/>
+      <c r="P56" s="95"/>
+      <c r="Q56" s="95"/>
+      <c r="R56" s="95"/>
+      <c r="S56" s="95"/>
+      <c r="T56" s="95"/>
+      <c r="U56" s="95"/>
+      <c r="V56" s="95"/>
+      <c r="W56" s="95"/>
       <c r="X56" s="4"/>
       <c r="Y56" s="5"/>
     </row>
     <row r="57" spans="1:28" ht="24" customHeight="1">
-      <c r="A57" s="56"/>
-      <c r="B57" s="58" t="s">
+      <c r="A57" s="64"/>
+      <c r="B57" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="61"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="61"/>
-      <c r="J57" s="61"/>
-      <c r="K57" s="61"/>
-      <c r="L57" s="61"/>
-      <c r="M57" s="61"/>
-      <c r="N57" s="61"/>
-      <c r="O57" s="61"/>
-      <c r="P57" s="61"/>
-      <c r="Q57" s="61"/>
-      <c r="R57" s="61"/>
-      <c r="S57" s="61"/>
-      <c r="T57" s="61"/>
-      <c r="U57" s="61"/>
-      <c r="V57" s="61"/>
-      <c r="W57" s="61"/>
-      <c r="X57" s="61"/>
-      <c r="Y57" s="62"/>
+      <c r="C57" s="93"/>
+      <c r="D57" s="93"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="26"/>
+      <c r="Q57" s="26"/>
+      <c r="R57" s="26"/>
+      <c r="S57" s="26"/>
+      <c r="T57" s="26"/>
+      <c r="U57" s="26"/>
+      <c r="V57" s="26"/>
+      <c r="W57" s="26"/>
+      <c r="X57" s="26"/>
+      <c r="Y57" s="96"/>
     </row>
     <row r="58" spans="1:28" ht="26" customHeight="1">
-      <c r="A58" s="56"/>
-      <c r="B58" s="58" t="s">
+      <c r="A58" s="64"/>
+      <c r="B58" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="61"/>
-      <c r="J58" s="61"/>
-      <c r="K58" s="61"/>
-      <c r="L58" s="61"/>
-      <c r="M58" s="61"/>
-      <c r="N58" s="61"/>
-      <c r="O58" s="61"/>
-      <c r="P58" s="61"/>
-      <c r="Q58" s="61"/>
-      <c r="R58" s="61"/>
-      <c r="S58" s="61"/>
-      <c r="T58" s="61"/>
-      <c r="U58" s="61"/>
-      <c r="V58" s="61"/>
-      <c r="W58" s="61"/>
-      <c r="X58" s="61"/>
-      <c r="Y58" s="62"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="93"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="26"/>
+      <c r="O58" s="26"/>
+      <c r="P58" s="26"/>
+      <c r="Q58" s="26"/>
+      <c r="R58" s="26"/>
+      <c r="S58" s="26"/>
+      <c r="T58" s="26"/>
+      <c r="U58" s="26"/>
+      <c r="V58" s="26"/>
+      <c r="W58" s="26"/>
+      <c r="X58" s="26"/>
+      <c r="Y58" s="96"/>
     </row>
     <row r="59" spans="1:28" ht="23" customHeight="1">
-      <c r="A59" s="56"/>
-      <c r="B59" s="58" t="s">
+      <c r="A59" s="64"/>
+      <c r="B59" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="61"/>
-      <c r="J59" s="61"/>
-      <c r="K59" s="61"/>
-      <c r="L59" s="61"/>
-      <c r="M59" s="61"/>
-      <c r="N59" s="61"/>
-      <c r="O59" s="61"/>
-      <c r="P59" s="61"/>
-      <c r="Q59" s="61"/>
-      <c r="R59" s="61"/>
-      <c r="S59" s="61"/>
-      <c r="T59" s="61"/>
-      <c r="U59" s="61"/>
-      <c r="V59" s="61"/>
-      <c r="W59" s="61"/>
-      <c r="X59" s="61"/>
-      <c r="Y59" s="62"/>
+      <c r="C59" s="93"/>
+      <c r="D59" s="93"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="26"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="26"/>
+      <c r="Q59" s="26"/>
+      <c r="R59" s="26"/>
+      <c r="S59" s="26"/>
+      <c r="T59" s="26"/>
+      <c r="U59" s="26"/>
+      <c r="V59" s="26"/>
+      <c r="W59" s="26"/>
+      <c r="X59" s="26"/>
+      <c r="Y59" s="96"/>
     </row>
     <row r="60" spans="1:28" ht="26" customHeight="1" thickBot="1">
-      <c r="A60" s="56"/>
-      <c r="B60" s="59"/>
-      <c r="C60" s="59"/>
-      <c r="D60" s="59"/>
+      <c r="A60" s="64"/>
+      <c r="B60" s="94"/>
+      <c r="C60" s="94"/>
+      <c r="D60" s="94"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -4188,83 +4185,186 @@
       <c r="Y60" s="2"/>
     </row>
     <row r="69" spans="2:25">
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-      <c r="K69" s="20"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="20"/>
-      <c r="N69" s="20"/>
-      <c r="O69" s="20"/>
-      <c r="P69" s="20"/>
-      <c r="Q69" s="20"/>
-      <c r="R69" s="20"/>
-      <c r="S69" s="20"/>
-      <c r="T69" s="20"/>
-      <c r="U69" s="20"/>
-      <c r="V69" s="20"/>
-      <c r="W69" s="20"/>
-      <c r="X69" s="20"/>
-      <c r="Y69" s="20"/>
+      <c r="C69" s="98"/>
+      <c r="D69" s="98"/>
+      <c r="E69" s="98"/>
+      <c r="F69" s="98"/>
+      <c r="G69" s="98"/>
+      <c r="H69" s="98"/>
+      <c r="I69" s="98"/>
+      <c r="J69" s="98"/>
+      <c r="K69" s="98"/>
+      <c r="L69" s="98"/>
+      <c r="M69" s="98"/>
+      <c r="N69" s="98"/>
+      <c r="O69" s="98"/>
+      <c r="P69" s="98"/>
+      <c r="Q69" s="98"/>
+      <c r="R69" s="98"/>
+      <c r="S69" s="98"/>
+      <c r="T69" s="98"/>
+      <c r="U69" s="98"/>
+      <c r="V69" s="98"/>
+      <c r="W69" s="98"/>
+      <c r="X69" s="98"/>
+      <c r="Y69" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="223">
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="X34:Y34"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="X37:Y37"/>
-    <mergeCell ref="X38:Y38"/>
-    <mergeCell ref="X39:Y39"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="X26:Y27"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AB26:AB27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="T47:U47"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="X49:Y49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="X50:Y50"/>
-    <mergeCell ref="AB41:AB42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="X43:Y43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="B69:Y69"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C52:X54"/>
+    <mergeCell ref="B43:B50"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D47:D50"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="F47:F50"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E56:W56"/>
+    <mergeCell ref="E57:Y57"/>
+    <mergeCell ref="E58:Y58"/>
+    <mergeCell ref="E59:Y59"/>
+    <mergeCell ref="V26:V27"/>
+    <mergeCell ref="W26:W27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:P26"/>
+    <mergeCell ref="G47:G50"/>
+    <mergeCell ref="V41:V42"/>
+    <mergeCell ref="W41:W42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="T46:U46"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L41:P41"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="A26:A39"/>
+    <mergeCell ref="B6:B13"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="D32:D39"/>
+    <mergeCell ref="E32:E39"/>
+    <mergeCell ref="F28:F39"/>
+    <mergeCell ref="G32:G39"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:P4"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="A15:A24"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="X15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="T19:U19"/>
     <mergeCell ref="X23:Y23"/>
     <mergeCell ref="R24:S24"/>
     <mergeCell ref="T24:U24"/>
@@ -4289,157 +4389,54 @@
     <mergeCell ref="X29:Y29"/>
     <mergeCell ref="X30:Y30"/>
     <mergeCell ref="R26:U26"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="AB15:AB16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="X15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="A15:A24"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A4:A13"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:P4"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="A26:A39"/>
-    <mergeCell ref="B6:B13"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="G28:G31"/>
-    <mergeCell ref="D32:D39"/>
-    <mergeCell ref="E32:E39"/>
-    <mergeCell ref="F28:F39"/>
-    <mergeCell ref="G32:G39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L41:P41"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="A41:A50"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E56:W56"/>
-    <mergeCell ref="E57:Y57"/>
-    <mergeCell ref="E58:Y58"/>
-    <mergeCell ref="E59:Y59"/>
-    <mergeCell ref="V26:V27"/>
-    <mergeCell ref="W26:W27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:P26"/>
-    <mergeCell ref="G47:G50"/>
-    <mergeCell ref="V41:V42"/>
-    <mergeCell ref="W41:W42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="B69:Y69"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C52:X54"/>
-    <mergeCell ref="B43:B50"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D47:D50"/>
-    <mergeCell ref="E47:E50"/>
-    <mergeCell ref="F47:F50"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="AB41:AB42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="X43:Y43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="T47:U47"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="X48:Y48"/>
+    <mergeCell ref="X49:Y49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="X26:Y27"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AB26:AB27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="X37:Y37"/>
+    <mergeCell ref="X38:Y38"/>
+    <mergeCell ref="X39:Y39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="5">
@@ -4487,884 +4484,874 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.5" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="93" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="96"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="E4" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="97" t="s">
+      <c r="F4" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="97" t="s">
+      <c r="G4" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="97" t="s">
+      <c r="H4" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="98"/>
-      <c r="J4" s="99"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="97" t="s">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="100">
+      <c r="D5" s="21">
         <v>77</v>
       </c>
-      <c r="E5" s="100">
+      <c r="E5" s="21">
         <v>77</v>
       </c>
-      <c r="F5" s="100">
+      <c r="F5" s="21">
         <v>77</v>
       </c>
-      <c r="G5" s="100">
+      <c r="G5" s="21">
         <v>77</v>
       </c>
-      <c r="H5" s="100">
+      <c r="H5" s="21">
         <v>77</v>
       </c>
-      <c r="I5" s="101"/>
-      <c r="J5" s="99"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="97" t="s">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="100">
+      <c r="D6" s="21">
         <v>78</v>
       </c>
-      <c r="E6" s="100">
+      <c r="E6" s="21">
         <v>118</v>
       </c>
-      <c r="F6" s="100">
+      <c r="F6" s="21">
         <v>227</v>
       </c>
-      <c r="G6" s="100">
+      <c r="G6" s="21">
         <v>78</v>
       </c>
-      <c r="H6" s="100">
+      <c r="H6" s="21">
         <v>78</v>
       </c>
-      <c r="I6" s="101"/>
-      <c r="J6" s="99"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="97" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="100">
+      <c r="D7" s="21">
         <v>4</v>
       </c>
-      <c r="E7" s="100">
+      <c r="E7" s="21">
         <v>4</v>
       </c>
-      <c r="F7" s="100">
+      <c r="F7" s="21">
         <v>0</v>
       </c>
-      <c r="G7" s="100">
+      <c r="G7" s="21">
         <v>4</v>
       </c>
-      <c r="H7" s="100">
+      <c r="H7" s="21">
         <v>4</v>
       </c>
-      <c r="I7" s="101"/>
-      <c r="J7" s="99"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="61"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="97" t="s">
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="100" t="s">
+      <c r="D8" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="100" t="s">
+      <c r="E8" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="100" t="s">
+      <c r="F8" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="100" t="s">
+      <c r="G8" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="100" t="s">
+      <c r="H8" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="101"/>
-      <c r="J8" s="99"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="35"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="61"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="97" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="100" t="s">
+      <c r="D9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="100" t="s">
+      <c r="E9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="100" t="s">
+      <c r="F9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="100" t="s">
+      <c r="G9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="100" t="s">
+      <c r="H9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="101"/>
-      <c r="J9" s="99"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="61"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="97" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="102" t="s">
+      <c r="D10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="102" t="s">
+      <c r="F10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="102" t="s">
+      <c r="G10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="102" t="s">
+      <c r="H10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="103"/>
-      <c r="J10" s="99"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="61"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="93" t="s">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="99"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="35"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="61"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="97" t="s">
+      <c r="E12" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="97" t="s">
+      <c r="F12" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="97" t="s">
+      <c r="G12" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H12" s="97" t="s">
+      <c r="H12" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="I12" s="98"/>
-      <c r="J12" s="99"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="35"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="61"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="97" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="100">
+      <c r="D13" s="21">
         <v>67</v>
       </c>
-      <c r="E13" s="100">
+      <c r="E13" s="21">
         <v>67</v>
       </c>
-      <c r="F13" s="100">
+      <c r="F13" s="21">
         <v>67</v>
       </c>
-      <c r="G13" s="100">
+      <c r="G13" s="21">
         <v>77</v>
       </c>
-      <c r="H13" s="100">
+      <c r="H13" s="21">
         <v>77</v>
       </c>
-      <c r="I13" s="101"/>
-      <c r="J13" s="99"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="61"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="97" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="100">
+      <c r="D14" s="21">
         <v>23</v>
       </c>
-      <c r="E14" s="100">
+      <c r="E14" s="21">
         <v>73</v>
       </c>
-      <c r="F14" s="100">
+      <c r="F14" s="21">
         <v>289</v>
       </c>
-      <c r="G14" s="100">
+      <c r="G14" s="21">
         <v>77</v>
       </c>
-      <c r="H14" s="100">
+      <c r="H14" s="21">
         <v>79</v>
       </c>
-      <c r="I14" s="101"/>
-      <c r="J14" s="99"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="35"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="61"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="97" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="100">
+      <c r="D15" s="21">
         <v>0</v>
       </c>
-      <c r="E15" s="100">
+      <c r="E15" s="21">
         <v>4</v>
       </c>
-      <c r="F15" s="100">
+      <c r="F15" s="21">
         <v>9</v>
       </c>
-      <c r="G15" s="100">
+      <c r="G15" s="21">
         <v>2</v>
       </c>
-      <c r="H15" s="100">
+      <c r="H15" s="21">
         <v>4</v>
       </c>
-      <c r="I15" s="101"/>
-      <c r="J15" s="99"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="61"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="97" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="100">
+      <c r="D16" s="21">
         <v>2</v>
       </c>
-      <c r="E16" s="100">
+      <c r="E16" s="21">
         <v>4</v>
       </c>
-      <c r="F16" s="100">
+      <c r="F16" s="21">
         <v>6</v>
       </c>
-      <c r="G16" s="100" t="s">
+      <c r="G16" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="H16" s="100" t="s">
+      <c r="H16" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="101"/>
-      <c r="J16" s="99"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="35"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="61"/>
-      <c r="B17" s="61"/>
-      <c r="C17" s="97" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="100" t="s">
+      <c r="D17" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="100" t="s">
+      <c r="E17" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="100" t="s">
+      <c r="F17" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="100" t="s">
+      <c r="G17" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="H17" s="100" t="s">
+      <c r="H17" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="I17" s="101"/>
-      <c r="J17" s="99"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="61"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="97" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="102">
+      <c r="D18" s="23">
         <v>11451479</v>
       </c>
-      <c r="E18" s="102">
+      <c r="E18" s="23">
         <v>11451479</v>
       </c>
-      <c r="F18" s="102">
+      <c r="F18" s="23">
         <v>11451479</v>
       </c>
-      <c r="G18" s="102" t="s">
+      <c r="G18" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H18" s="102" t="s">
+      <c r="H18" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="I18" s="103"/>
-      <c r="J18" s="99"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="93" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="99"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="61"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="97" t="s">
+      <c r="E20" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="97" t="s">
+      <c r="F20" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="97" t="s">
+      <c r="G20" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H20" s="97" t="s">
+      <c r="H20" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="I20" s="98"/>
-      <c r="J20" s="99"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="61"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="97" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="100">
+      <c r="D21" s="21">
         <v>56</v>
       </c>
-      <c r="E21" s="100">
+      <c r="E21" s="21">
         <v>56</v>
       </c>
-      <c r="F21" s="100">
+      <c r="F21" s="21">
         <v>57</v>
       </c>
-      <c r="G21" s="100">
+      <c r="G21" s="21">
         <v>58</v>
       </c>
-      <c r="H21" s="100">
+      <c r="H21" s="21">
         <v>56</v>
       </c>
-      <c r="I21" s="101"/>
-      <c r="J21" s="99"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="35"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="61"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="97" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="100">
+      <c r="D22" s="21">
         <v>40</v>
       </c>
-      <c r="E22" s="100">
+      <c r="E22" s="21">
         <v>20</v>
       </c>
-      <c r="F22" s="100">
+      <c r="F22" s="21">
         <v>60</v>
       </c>
-      <c r="G22" s="100">
+      <c r="G22" s="21">
         <v>22</v>
       </c>
-      <c r="H22" s="100">
+      <c r="H22" s="21">
         <v>19</v>
       </c>
-      <c r="I22" s="101"/>
-      <c r="J22" s="99"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="61"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="97" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="100">
+      <c r="D23" s="21">
         <v>8</v>
       </c>
-      <c r="E23" s="100">
+      <c r="E23" s="21">
         <v>0</v>
       </c>
-      <c r="F23" s="100">
+      <c r="F23" s="21">
         <v>0</v>
       </c>
-      <c r="G23" s="100">
+      <c r="G23" s="21">
         <v>0</v>
       </c>
-      <c r="H23" s="100">
+      <c r="H23" s="21">
         <v>2</v>
       </c>
-      <c r="I23" s="101"/>
-      <c r="J23" s="99"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="35"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="61"/>
-      <c r="B24" s="61"/>
-      <c r="C24" s="97" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="104" t="s">
+      <c r="D24" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="105" t="s">
+      <c r="E24" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="100" t="s">
+      <c r="F24" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="G24" s="100" t="s">
+      <c r="G24" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="H24" s="100" t="s">
+      <c r="H24" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="I24" s="101"/>
-      <c r="J24" s="99"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="35"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="61"/>
-      <c r="B25" s="61"/>
-      <c r="C25" s="97" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="100" t="s">
+      <c r="D25" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="100" t="s">
+      <c r="E25" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="100" t="s">
+      <c r="F25" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="G25" s="100" t="s">
+      <c r="G25" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="100" t="s">
+      <c r="H25" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="I25" s="101"/>
-      <c r="J25" s="99"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="35"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="61"/>
-      <c r="B26" s="61"/>
-      <c r="C26" s="97" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="102">
+      <c r="D26" s="23">
         <v>11451589</v>
       </c>
-      <c r="E26" s="102">
+      <c r="E26" s="23">
         <v>11451589</v>
       </c>
-      <c r="F26" s="102">
+      <c r="F26" s="23">
         <v>11451589</v>
       </c>
-      <c r="G26" s="102">
+      <c r="G26" s="23">
         <v>11451589</v>
       </c>
-      <c r="H26" s="102" t="s">
+      <c r="H26" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="I26" s="103"/>
-      <c r="J26" s="99"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="35"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="61"/>
-      <c r="B27" s="61"/>
-      <c r="C27" s="93" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="99"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="35"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="61"/>
-      <c r="B28" s="61"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97" t="s">
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="97" t="s">
+      <c r="E28" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="97" t="s">
+      <c r="F28" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="97" t="s">
+      <c r="G28" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="97" t="s">
+      <c r="H28" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="I28" s="98"/>
-      <c r="J28" s="99"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="35"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="61"/>
-      <c r="B29" s="61"/>
-      <c r="C29" s="97" t="s">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="100">
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21">
         <v>78</v>
       </c>
-      <c r="H29" s="100">
+      <c r="H29" s="21">
         <v>78</v>
       </c>
-      <c r="I29" s="101"/>
-      <c r="J29" s="99"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="35"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="61"/>
-      <c r="B30" s="61"/>
-      <c r="C30" s="97" t="s">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="100"/>
-      <c r="G30" s="100">
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21">
         <v>59</v>
       </c>
-      <c r="H30" s="100">
+      <c r="H30" s="21">
         <v>59</v>
       </c>
-      <c r="I30" s="101"/>
-      <c r="J30" s="99"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="35"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="97" t="s">
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="100">
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21">
         <v>8</v>
       </c>
-      <c r="H31" s="100">
+      <c r="H31" s="21">
         <v>8</v>
       </c>
-      <c r="I31" s="101"/>
-      <c r="J31" s="99"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="35"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="61"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="97" t="s">
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="100"/>
-      <c r="G32" s="100" t="s">
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="100" t="s">
+      <c r="H32" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="I32" s="101"/>
-      <c r="J32" s="99"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="35"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="61"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="97" t="s">
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="100" t="s">
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="H33" s="100" t="s">
+      <c r="H33" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="I33" s="101"/>
-      <c r="J33" s="99"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="35"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="61"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="97" t="s">
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102" t="s">
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="102" t="s">
+      <c r="H34" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="I34" s="103"/>
-      <c r="J34" s="99"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="35"/>
     </row>
     <row r="35" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A35" s="106" t="s">
+      <c r="A35" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="107"/>
-      <c r="C35" s="97" t="s">
+      <c r="B35" s="30"/>
+      <c r="C35" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="101">
+      <c r="D35" s="22">
         <v>32</v>
       </c>
-      <c r="E35" s="101" t="s">
+      <c r="E35" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="101">
+      <c r="F35" s="22">
         <v>22</v>
       </c>
-      <c r="G35" s="101" t="s">
+      <c r="G35" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H35" s="101">
+      <c r="H35" s="22">
         <v>22</v>
       </c>
-      <c r="I35" s="101" t="s">
+      <c r="I35" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="J35" s="101" t="s">
+      <c r="J35" s="22" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="34.75" customHeight="1">
-      <c r="A36" s="61" t="s">
+      <c r="A36" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="61"/>
-      <c r="C36" s="97" t="s">
+      <c r="B36" s="26"/>
+      <c r="C36" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="101">
+      <c r="D36" s="22">
         <v>2</v>
       </c>
-      <c r="E36" s="101" t="s">
+      <c r="E36" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="F36" s="101">
+      <c r="F36" s="22">
         <v>2</v>
       </c>
-      <c r="G36" s="101" t="s">
+      <c r="G36" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H36" s="101">
+      <c r="H36" s="22">
         <v>2</v>
       </c>
-      <c r="I36" s="101" t="s">
+      <c r="I36" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="J36" s="101" t="s">
+      <c r="J36" s="22" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="93" t="s">
+      <c r="A37" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="94"/>
-      <c r="C37" s="94"/>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="94"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="94"/>
-      <c r="J37" s="94"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
     </row>
     <row r="38" spans="1:10" ht="26" customHeight="1">
-      <c r="A38" s="101"/>
-      <c r="B38" s="101"/>
-      <c r="C38" s="101"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="101"/>
-      <c r="F38" s="101"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
     </row>
     <row r="39" spans="1:10" ht="37" customHeight="1">
-      <c r="A39" s="101"/>
-      <c r="B39" s="101"/>
-      <c r="C39" s="101"/>
-      <c r="D39" s="101"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="101"/>
-      <c r="B40" s="101"/>
-      <c r="C40" s="101"/>
-      <c r="D40" s="101"/>
-      <c r="E40" s="101"/>
-      <c r="F40" s="101"/>
-      <c r="G40" s="101"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="101"/>
-      <c r="B41" s="101"/>
-      <c r="C41" s="101"/>
-      <c r="D41" s="101"/>
-      <c r="E41" s="101"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="101"/>
-      <c r="B42" s="101"/>
-      <c r="C42" s="101"/>
-      <c r="D42" s="101"/>
-      <c r="E42" s="101"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="101"/>
-      <c r="B43" s="101"/>
-      <c r="C43" s="101"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="101"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
-      <c r="J43" s="61"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="F42:J42"/>
-    <mergeCell ref="F43:J43"/>
-    <mergeCell ref="F44:J44"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="G38:J38"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -5373,6 +5360,16 @@
     <mergeCell ref="C11:I11"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="F42:J42"/>
+    <mergeCell ref="F43:J43"/>
+    <mergeCell ref="F44:J44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ws_test_file_use.xlsx
+++ b/ws_test_file_use.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuechen/PycharmProjects/excel_agent_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B80B99-465C-7344-BDA0-E4F5F876B0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E532172-BCCB-D94C-B31F-A020227DAF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="20640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIGURATION" sheetId="1" r:id="rId1"/>
     <sheet name="WL_56A0DS6" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="MW_56A0DS6" sheetId="3" r:id="rId3"/>
+    <sheet name="Power Load Information_56A0DS6" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">CONFIGURATION!$A$1:$AC$83</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="147">
   <si>
     <t xml:space="preserve">SYSTEM MODULE </t>
   </si>
@@ -394,22 +395,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Leg1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leg2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leg3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leg4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RF Free Pole(pcs)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -423,6 +408,187 @@
   </si>
   <si>
     <t>8/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MW Survey Report</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. MW Antenna Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antenna Size &amp; Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antenna Polaraization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MWLink 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MWLink 2</t>
+  </si>
+  <si>
+    <t>MWLink 3</t>
+  </si>
+  <si>
+    <t>MWLink 4</t>
+  </si>
+  <si>
+    <t>MWLink 5</t>
+  </si>
+  <si>
+    <t>MWLink 6</t>
+  </si>
+  <si>
+    <t>A350-900HAC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Space Available for New MW Antenna(m)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MW Free Pole(pcs)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. MW RTN(IDU) Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exiting RTN Location, Quantity &amp; Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Location</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quantity &amp; type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remarks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Load Information Survey Report</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. DCDU 14B Load Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCDU 14B Load Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fuse Capacity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCDU 1 Port Information</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCDU 2 Port Information</t>
+  </si>
+  <si>
+    <t>DCDU 3 Port Information</t>
+  </si>
+  <si>
+    <t>Load 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Load 1</t>
+  </si>
+  <si>
+    <t>Load 2</t>
+  </si>
+  <si>
+    <t>Load 3</t>
+  </si>
+  <si>
+    <t>Load 4</t>
+  </si>
+  <si>
+    <t>Load 5</t>
+  </si>
+  <si>
+    <t>Load 6</t>
+  </si>
+  <si>
+    <t>Load 7</t>
+  </si>
+  <si>
+    <t>Load 8</t>
+  </si>
+  <si>
+    <t>Load 9</t>
+  </si>
+  <si>
+    <t>99A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIRBUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A359</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Distance to
+Power cabinet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29" Rock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Apple Power System</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,7 +596,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -527,6 +693,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1075,7 +1258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1157,10 +1340,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1169,35 +1364,200 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1205,15 +1565,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1229,172 +1580,61 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1817,112 +2057,112 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="76"/>
-      <c r="Y2" s="76"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+      <c r="X2" s="97"/>
+      <c r="Y2" s="97"/>
     </row>
     <row r="3" spans="1:28" ht="15" thickBot="1"/>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="67" t="s">
+      <c r="E4" s="39"/>
+      <c r="F4" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="59" t="s">
+      <c r="I4" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59" t="s">
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="77" t="s">
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="59" t="s">
+      <c r="R4" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="59"/>
-      <c r="V4" s="43" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="W4" s="43" t="s">
+      <c r="W4" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="39" t="s">
+      <c r="X4" s="44" t="s">
         <v>49</v>
       </c>
       <c r="Y4" s="40"/>
       <c r="Z4" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="43" t="s">
+      <c r="AA4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="45" t="s">
+      <c r="AB4" s="46" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="26" customHeight="1">
-      <c r="A5" s="64"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
+      <c r="A5" s="73"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
       <c r="D5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
       <c r="I5" s="7" t="s">
         <v>10</v>
       </c>
@@ -1947,32 +2187,32 @@
       <c r="P5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="55" t="s">
+      <c r="Q5" s="86"/>
+      <c r="R5" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="S5" s="56"/>
-      <c r="T5" s="57" t="s">
+      <c r="S5" s="49"/>
+      <c r="T5" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="U5" s="58"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="60"/>
-      <c r="Y5" s="61"/>
-      <c r="Z5" s="61"/>
-      <c r="AA5" s="62"/>
-      <c r="AB5" s="54"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="43"/>
+      <c r="AB5" s="47"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="64"/>
-      <c r="B6" s="82" t="s">
+      <c r="A6" s="73"/>
+      <c r="B6" s="60" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="8">
         <v>1</v>
       </c>
-      <c r="D6" s="38"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1986,25 +2226,25 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="9"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="37"/>
+      <c r="X6" s="70"/>
+      <c r="Y6" s="71"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="14"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="64"/>
-      <c r="B7" s="83"/>
+      <c r="A7" s="73"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="8">
         <v>2</v>
       </c>
-      <c r="D7" s="38"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -2018,25 +2258,25 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="9"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="37"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="71"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="14"/>
     </row>
     <row r="8" spans="1:28">
-      <c r="A8" s="64"/>
-      <c r="B8" s="83"/>
+      <c r="A8" s="73"/>
+      <c r="B8" s="61"/>
       <c r="C8" s="8">
         <v>3</v>
       </c>
-      <c r="D8" s="38"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2050,25 +2290,25 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="9"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
       <c r="V8" s="8"/>
       <c r="W8" s="8"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="37"/>
+      <c r="X8" s="70"/>
+      <c r="Y8" s="71"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="14"/>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="64"/>
-      <c r="B9" s="83"/>
+      <c r="A9" s="73"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="8">
         <v>4</v>
       </c>
-      <c r="D9" s="38"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -2082,34 +2322,34 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="9"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
       <c r="V9" s="8"/>
       <c r="W9" s="8"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="37"/>
+      <c r="X9" s="70"/>
+      <c r="Y9" s="71"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="14"/>
     </row>
     <row r="10" spans="1:28">
-      <c r="A10" s="64"/>
-      <c r="B10" s="83"/>
+      <c r="A10" s="73"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="8">
         <v>1</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="71">
+      <c r="E10" s="65">
         <v>3</v>
       </c>
-      <c r="F10" s="74" t="s">
+      <c r="F10" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="74" t="s">
+      <c r="G10" s="68" t="s">
         <v>31</v>
       </c>
       <c r="H10" s="10">
@@ -2142,22 +2382,22 @@
       <c r="Q10" s="11">
         <v>50</v>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="36">
         <v>0</v>
       </c>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38">
+      <c r="S10" s="36"/>
+      <c r="T10" s="36">
         <v>0</v>
       </c>
-      <c r="U10" s="38"/>
+      <c r="U10" s="36"/>
       <c r="V10" s="8">
         <v>5</v>
       </c>
       <c r="W10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="37"/>
+      <c r="X10" s="70"/>
+      <c r="Y10" s="71"/>
       <c r="Z10" s="8" t="s">
         <v>26</v>
       </c>
@@ -2167,15 +2407,15 @@
       <c r="AB10" s="14"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="64"/>
-      <c r="B11" s="83"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="8">
         <v>2</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
       <c r="H11" s="8">
         <v>3</v>
       </c>
@@ -2206,22 +2446,22 @@
       <c r="Q11" s="9">
         <v>130</v>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="36">
         <v>0</v>
       </c>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38">
+      <c r="S11" s="36"/>
+      <c r="T11" s="36">
         <v>0</v>
       </c>
-      <c r="U11" s="38"/>
+      <c r="U11" s="36"/>
       <c r="V11" s="8">
         <v>5</v>
       </c>
       <c r="W11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="37"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="71"/>
       <c r="Z11" s="8" t="s">
         <v>26</v>
       </c>
@@ -2231,15 +2471,15 @@
       <c r="AB11" s="14"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="64"/>
-      <c r="B12" s="83"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -2250,28 +2490,28 @@
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="9"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="37"/>
+      <c r="X12" s="70"/>
+      <c r="Y12" s="71"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="15"/>
       <c r="AB12" s="14"/>
     </row>
     <row r="13" spans="1:28" ht="15" thickBot="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="84"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="62"/>
       <c r="C13" s="12">
         <v>4</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
@@ -2282,96 +2522,96 @@
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="13"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="51"/>
-      <c r="U13" s="51"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="69"/>
+      <c r="U13" s="69"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="53"/>
+      <c r="X13" s="98"/>
+      <c r="Y13" s="99"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="12"/>
       <c r="AB13" s="16"/>
     </row>
     <row r="14" spans="1:28" ht="15" thickBot="1"/>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="59"/>
-      <c r="F15" s="67" t="s">
+      <c r="E15" s="39"/>
+      <c r="F15" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="G15" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="67" t="s">
+      <c r="H15" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="59" t="s">
+      <c r="I15" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="59"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="59" t="s">
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="77" t="s">
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="59" t="s">
+      <c r="R15" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="S15" s="59"/>
-      <c r="T15" s="59"/>
-      <c r="U15" s="59"/>
-      <c r="V15" s="43" t="s">
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+      <c r="V15" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="W15" s="43" t="s">
+      <c r="W15" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="X15" s="39" t="s">
+      <c r="X15" s="44" t="s">
         <v>49</v>
       </c>
       <c r="Y15" s="40"/>
       <c r="Z15" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA15" s="43" t="s">
+      <c r="AA15" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="AB15" s="45" t="s">
+      <c r="AB15" s="46" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="26" customHeight="1">
-      <c r="A16" s="64"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
       <c r="D16" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
       <c r="I16" s="7" t="s">
         <v>10</v>
       </c>
@@ -2396,32 +2636,32 @@
       <c r="P16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="55" t="s">
+      <c r="Q16" s="86"/>
+      <c r="R16" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="S16" s="56"/>
-      <c r="T16" s="57" t="s">
+      <c r="S16" s="49"/>
+      <c r="T16" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="U16" s="58"/>
-      <c r="V16" s="62"/>
-      <c r="W16" s="62"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="61"/>
-      <c r="Z16" s="61"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="54"/>
+      <c r="U16" s="51"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="45"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="41"/>
+      <c r="AA16" s="43"/>
+      <c r="AB16" s="47"/>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="64"/>
-      <c r="B17" s="82" t="s">
+      <c r="A17" s="73"/>
+      <c r="B17" s="60" t="s">
         <v>58</v>
       </c>
       <c r="C17" s="8">
         <v>1</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="36" t="s">
         <v>59</v>
       </c>
       <c r="E17" s="8">
@@ -2463,22 +2703,22 @@
       <c r="Q17" s="9">
         <v>50</v>
       </c>
-      <c r="R17" s="38">
+      <c r="R17" s="36">
         <v>0</v>
       </c>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38">
+      <c r="S17" s="36"/>
+      <c r="T17" s="36">
         <v>0</v>
       </c>
-      <c r="U17" s="38"/>
+      <c r="U17" s="36"/>
       <c r="V17" s="8">
         <v>5</v>
       </c>
       <c r="W17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="37"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="71"/>
       <c r="Z17" s="8" t="s">
         <v>22</v>
       </c>
@@ -2486,12 +2726,12 @@
       <c r="AB17" s="14"/>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="64"/>
-      <c r="B18" s="83"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="61"/>
       <c r="C18" s="8">
         <v>2</v>
       </c>
-      <c r="D18" s="38"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -2525,22 +2765,22 @@
       <c r="Q18" s="9">
         <v>50</v>
       </c>
-      <c r="R18" s="38">
+      <c r="R18" s="36">
         <v>0</v>
       </c>
-      <c r="S18" s="38"/>
-      <c r="T18" s="38">
+      <c r="S18" s="36"/>
+      <c r="T18" s="36">
         <v>0</v>
       </c>
-      <c r="U18" s="38"/>
+      <c r="U18" s="36"/>
       <c r="V18" s="8">
         <v>5</v>
       </c>
       <c r="W18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="37"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="71"/>
       <c r="Z18" s="8" t="s">
         <v>22</v>
       </c>
@@ -2548,12 +2788,12 @@
       <c r="AB18" s="14"/>
     </row>
     <row r="19" spans="1:28">
-      <c r="A19" s="64"/>
-      <c r="B19" s="83"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="8">
         <v>3</v>
       </c>
-      <c r="D19" s="38"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -2567,25 +2807,25 @@
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="9"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="38"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="38"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="37"/>
+      <c r="X19" s="70"/>
+      <c r="Y19" s="71"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="14"/>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="64"/>
-      <c r="B20" s="83"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="8">
         <v>4</v>
       </c>
-      <c r="D20" s="38"/>
+      <c r="D20" s="36"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -2599,34 +2839,34 @@
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="9"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="37"/>
+      <c r="X20" s="70"/>
+      <c r="Y20" s="71"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="14"/>
     </row>
     <row r="21" spans="1:28" ht="14" customHeight="1">
-      <c r="A21" s="64"/>
-      <c r="B21" s="83"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="8">
         <v>1</v>
       </c>
-      <c r="D21" s="69" t="s">
+      <c r="D21" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="71">
+      <c r="E21" s="65">
         <v>3</v>
       </c>
-      <c r="F21" s="74" t="s">
+      <c r="F21" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="G21" s="74" t="s">
+      <c r="G21" s="68" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="10">
@@ -2659,22 +2899,22 @@
       <c r="Q21" s="11">
         <v>50</v>
       </c>
-      <c r="R21" s="38">
+      <c r="R21" s="36">
         <v>0</v>
       </c>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38">
+      <c r="S21" s="36"/>
+      <c r="T21" s="36">
         <v>0</v>
       </c>
-      <c r="U21" s="38"/>
+      <c r="U21" s="36"/>
       <c r="V21" s="8">
         <v>5</v>
       </c>
       <c r="W21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="37"/>
+      <c r="X21" s="70"/>
+      <c r="Y21" s="71"/>
       <c r="Z21" s="8" t="s">
         <v>26</v>
       </c>
@@ -2684,15 +2924,15 @@
       <c r="AB21" s="14"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="64"/>
-      <c r="B22" s="83"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="8">
         <v>2</v>
       </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
       <c r="H22" s="8">
         <v>3</v>
       </c>
@@ -2723,22 +2963,22 @@
       <c r="Q22" s="9">
         <v>130</v>
       </c>
-      <c r="R22" s="38">
+      <c r="R22" s="36">
         <v>0</v>
       </c>
-      <c r="S22" s="38"/>
-      <c r="T22" s="38">
+      <c r="S22" s="36"/>
+      <c r="T22" s="36">
         <v>0</v>
       </c>
-      <c r="U22" s="38"/>
+      <c r="U22" s="36"/>
       <c r="V22" s="8">
         <v>5</v>
       </c>
       <c r="W22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X22" s="36"/>
-      <c r="Y22" s="37"/>
+      <c r="X22" s="70"/>
+      <c r="Y22" s="71"/>
       <c r="Z22" s="8" t="s">
         <v>26</v>
       </c>
@@ -2748,15 +2988,15 @@
       <c r="AB22" s="14"/>
     </row>
     <row r="23" spans="1:28">
-      <c r="A23" s="64"/>
-      <c r="B23" s="83"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="61"/>
       <c r="C23" s="8">
         <v>3</v>
       </c>
-      <c r="D23" s="69"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
@@ -2767,28 +3007,28 @@
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="9"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
+      <c r="R23" s="36"/>
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
-      <c r="X23" s="36"/>
-      <c r="Y23" s="37"/>
+      <c r="X23" s="70"/>
+      <c r="Y23" s="71"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="15"/>
       <c r="AB23" s="14"/>
     </row>
     <row r="24" spans="1:28" ht="15" thickBot="1">
-      <c r="A24" s="65"/>
-      <c r="B24" s="84"/>
+      <c r="A24" s="82"/>
+      <c r="B24" s="62"/>
       <c r="C24" s="12">
         <v>4</v>
       </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
@@ -2799,96 +3039,96 @@
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
       <c r="Q24" s="13"/>
-      <c r="R24" s="51"/>
-      <c r="S24" s="51"/>
-      <c r="T24" s="51"/>
-      <c r="U24" s="51"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
-      <c r="X24" s="52"/>
-      <c r="Y24" s="53"/>
+      <c r="X24" s="98"/>
+      <c r="Y24" s="99"/>
       <c r="Z24" s="12"/>
       <c r="AA24" s="12"/>
       <c r="AB24" s="16"/>
     </row>
     <row r="25" spans="1:28" ht="15" thickBot="1"/>
     <row r="26" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A26" s="79" t="s">
+      <c r="A26" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="67" t="s">
+      <c r="E26" s="39"/>
+      <c r="F26" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="67" t="s">
+      <c r="G26" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="67" t="s">
+      <c r="H26" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="I26" s="59" t="s">
+      <c r="I26" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59" t="s">
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="59"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="77" t="s">
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="R26" s="59" t="s">
+      <c r="R26" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="S26" s="59"/>
-      <c r="T26" s="59"/>
-      <c r="U26" s="59"/>
-      <c r="V26" s="43" t="s">
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="W26" s="43" t="s">
+      <c r="W26" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="X26" s="39" t="s">
+      <c r="X26" s="44" t="s">
         <v>49</v>
       </c>
       <c r="Y26" s="40"/>
       <c r="Z26" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA26" s="43" t="s">
+      <c r="AA26" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="AB26" s="45" t="s">
+      <c r="AB26" s="46" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="26" customHeight="1">
-      <c r="A27" s="80"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="68"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="68"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
       <c r="I27" s="7" t="s">
         <v>10</v>
       </c>
@@ -2913,41 +3153,41 @@
       <c r="P27" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="Q27" s="91"/>
-      <c r="R27" s="47" t="s">
+      <c r="Q27" s="85"/>
+      <c r="R27" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="S27" s="48"/>
-      <c r="T27" s="49" t="s">
+      <c r="S27" s="104"/>
+      <c r="T27" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="U27" s="50"/>
-      <c r="V27" s="44"/>
-      <c r="W27" s="44"/>
-      <c r="X27" s="41"/>
-      <c r="Y27" s="42"/>
-      <c r="Z27" s="42"/>
-      <c r="AA27" s="44"/>
-      <c r="AB27" s="46"/>
+      <c r="U27" s="106"/>
+      <c r="V27" s="79"/>
+      <c r="W27" s="79"/>
+      <c r="X27" s="100"/>
+      <c r="Y27" s="101"/>
+      <c r="Z27" s="101"/>
+      <c r="AA27" s="79"/>
+      <c r="AB27" s="102"/>
     </row>
     <row r="28" spans="1:28">
-      <c r="A28" s="80"/>
-      <c r="B28" s="82" t="s">
+      <c r="A28" s="88"/>
+      <c r="B28" s="60" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="8">
         <v>1</v>
       </c>
-      <c r="D28" s="82" t="s">
+      <c r="D28" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="85">
+      <c r="E28" s="90">
         <v>1</v>
       </c>
-      <c r="F28" s="82" t="s">
+      <c r="F28" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="82" t="s">
+      <c r="G28" s="60" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="8">
@@ -2980,20 +3220,20 @@
       <c r="Q28" s="8">
         <v>50</v>
       </c>
-      <c r="R28" s="38">
+      <c r="R28" s="36">
         <v>0</v>
       </c>
-      <c r="S28" s="38"/>
-      <c r="T28" s="38">
+      <c r="S28" s="36"/>
+      <c r="T28" s="36">
         <v>0</v>
       </c>
-      <c r="U28" s="38"/>
+      <c r="U28" s="36"/>
       <c r="V28" s="8">
         <v>5</v>
       </c>
       <c r="W28" s="8"/>
-      <c r="X28" s="38"/>
-      <c r="Y28" s="38"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
       <c r="Z28" s="8" t="s">
         <v>22</v>
       </c>
@@ -3001,15 +3241,15 @@
       <c r="AB28" s="8"/>
     </row>
     <row r="29" spans="1:28">
-      <c r="A29" s="80"/>
-      <c r="B29" s="83"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="61"/>
       <c r="C29" s="8">
         <v>2</v>
       </c>
-      <c r="D29" s="83"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
       <c r="H29" s="8">
         <v>2</v>
       </c>
@@ -3040,20 +3280,20 @@
       <c r="Q29" s="8">
         <v>50</v>
       </c>
-      <c r="R29" s="38">
+      <c r="R29" s="36">
         <v>0</v>
       </c>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38">
+      <c r="S29" s="36"/>
+      <c r="T29" s="36">
         <v>0</v>
       </c>
-      <c r="U29" s="38"/>
+      <c r="U29" s="36"/>
       <c r="V29" s="8">
         <v>5</v>
       </c>
       <c r="W29" s="8"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
+      <c r="X29" s="36"/>
+      <c r="Y29" s="36"/>
       <c r="Z29" s="8" t="s">
         <v>22</v>
       </c>
@@ -3061,15 +3301,15 @@
       <c r="AB29" s="8"/>
     </row>
     <row r="30" spans="1:28">
-      <c r="A30" s="80"/>
-      <c r="B30" s="83"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="61"/>
       <c r="C30" s="8">
         <v>3</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
@@ -3080,28 +3320,28 @@
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
+      <c r="R30" s="36"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="36"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
-      <c r="X30" s="38"/>
-      <c r="Y30" s="38"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="36"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
     </row>
     <row r="31" spans="1:28">
-      <c r="A31" s="80"/>
-      <c r="B31" s="83"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="61"/>
       <c r="C31" s="8">
         <v>4</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="74"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="68"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
@@ -3112,32 +3352,32 @@
       <c r="O31" s="8"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="38"/>
-      <c r="S31" s="38"/>
-      <c r="T31" s="38"/>
-      <c r="U31" s="38"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
-      <c r="X31" s="38"/>
-      <c r="Y31" s="38"/>
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
     </row>
     <row r="32" spans="1:28">
-      <c r="A32" s="80"/>
-      <c r="B32" s="83"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="61"/>
       <c r="C32" s="8">
         <v>1</v>
       </c>
-      <c r="D32" s="87" t="s">
+      <c r="D32" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="85">
+      <c r="E32" s="90">
         <v>3</v>
       </c>
-      <c r="F32" s="83"/>
-      <c r="G32" s="82" t="s">
+      <c r="F32" s="61"/>
+      <c r="G32" s="60" t="s">
         <v>34</v>
       </c>
       <c r="H32" s="8">
@@ -3170,20 +3410,20 @@
       <c r="Q32" s="8">
         <v>50</v>
       </c>
-      <c r="R32" s="38">
+      <c r="R32" s="36">
         <v>0</v>
       </c>
-      <c r="S32" s="38"/>
-      <c r="T32" s="38">
+      <c r="S32" s="36"/>
+      <c r="T32" s="36">
         <v>0</v>
       </c>
-      <c r="U32" s="38"/>
+      <c r="U32" s="36"/>
       <c r="V32" s="8">
         <v>5</v>
       </c>
       <c r="W32" s="8"/>
-      <c r="X32" s="38"/>
-      <c r="Y32" s="38"/>
+      <c r="X32" s="36"/>
+      <c r="Y32" s="36"/>
       <c r="Z32" s="8" t="s">
         <v>26</v>
       </c>
@@ -3193,15 +3433,15 @@
       <c r="AB32" s="8"/>
     </row>
     <row r="33" spans="1:28">
-      <c r="A33" s="80"/>
-      <c r="B33" s="83"/>
+      <c r="A33" s="88"/>
+      <c r="B33" s="61"/>
       <c r="C33" s="8">
         <v>2</v>
       </c>
-      <c r="D33" s="88"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
       <c r="H33" s="8">
         <v>3</v>
       </c>
@@ -3232,20 +3472,20 @@
       <c r="Q33" s="8">
         <v>130</v>
       </c>
-      <c r="R33" s="38">
+      <c r="R33" s="36">
         <v>0</v>
       </c>
-      <c r="S33" s="38"/>
-      <c r="T33" s="38">
+      <c r="S33" s="36"/>
+      <c r="T33" s="36">
         <v>0</v>
       </c>
-      <c r="U33" s="38"/>
+      <c r="U33" s="36"/>
       <c r="V33" s="8">
         <v>5</v>
       </c>
       <c r="W33" s="8"/>
-      <c r="X33" s="38"/>
-      <c r="Y33" s="38"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="36"/>
       <c r="Z33" s="8" t="s">
         <v>26</v>
       </c>
@@ -3255,15 +3495,15 @@
       <c r="AB33" s="8"/>
     </row>
     <row r="34" spans="1:28">
-      <c r="A34" s="80"/>
-      <c r="B34" s="83"/>
+      <c r="A34" s="88"/>
+      <c r="B34" s="61"/>
       <c r="C34" s="8">
         <v>3</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
@@ -3274,28 +3514,28 @@
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
-      <c r="R34" s="38"/>
-      <c r="S34" s="38"/>
-      <c r="T34" s="38"/>
-      <c r="U34" s="38"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
-      <c r="X34" s="38"/>
-      <c r="Y34" s="38"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="36"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
     </row>
     <row r="35" spans="1:28">
-      <c r="A35" s="80"/>
-      <c r="B35" s="83"/>
+      <c r="A35" s="88"/>
+      <c r="B35" s="61"/>
       <c r="C35" s="8">
         <v>4</v>
       </c>
-      <c r="D35" s="88"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="91"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
@@ -3306,28 +3546,28 @@
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
-      <c r="R35" s="38"/>
-      <c r="S35" s="38"/>
-      <c r="T35" s="38"/>
-      <c r="U35" s="38"/>
+      <c r="R35" s="36"/>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="36"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
-      <c r="X35" s="38"/>
-      <c r="Y35" s="38"/>
+      <c r="X35" s="36"/>
+      <c r="Y35" s="36"/>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
     </row>
     <row r="36" spans="1:28">
-      <c r="A36" s="80"/>
-      <c r="B36" s="83"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="61"/>
       <c r="C36" s="8">
         <v>1</v>
       </c>
-      <c r="D36" s="88"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
       <c r="H36" s="8">
         <v>1</v>
       </c>
@@ -3358,20 +3598,20 @@
       <c r="Q36" s="8">
         <v>50</v>
       </c>
-      <c r="R36" s="38">
+      <c r="R36" s="36">
         <v>0</v>
       </c>
-      <c r="S36" s="38"/>
-      <c r="T36" s="38">
+      <c r="S36" s="36"/>
+      <c r="T36" s="36">
         <v>0</v>
       </c>
-      <c r="U36" s="38"/>
+      <c r="U36" s="36"/>
       <c r="V36" s="8">
         <v>5</v>
       </c>
       <c r="W36" s="8"/>
-      <c r="X36" s="38"/>
-      <c r="Y36" s="38"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
       <c r="Z36" s="8" t="s">
         <v>26</v>
       </c>
@@ -3381,15 +3621,15 @@
       <c r="AB36" s="8"/>
     </row>
     <row r="37" spans="1:28">
-      <c r="A37" s="80"/>
-      <c r="B37" s="83"/>
+      <c r="A37" s="88"/>
+      <c r="B37" s="61"/>
       <c r="C37" s="8">
         <v>2</v>
       </c>
-      <c r="D37" s="88"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
       <c r="H37" s="8">
         <v>1</v>
       </c>
@@ -3420,20 +3660,20 @@
       <c r="Q37" s="8">
         <v>130</v>
       </c>
-      <c r="R37" s="38">
+      <c r="R37" s="36">
         <v>0</v>
       </c>
-      <c r="S37" s="38"/>
-      <c r="T37" s="38">
+      <c r="S37" s="36"/>
+      <c r="T37" s="36">
         <v>0</v>
       </c>
-      <c r="U37" s="38"/>
+      <c r="U37" s="36"/>
       <c r="V37" s="8">
         <v>5</v>
       </c>
       <c r="W37" s="8"/>
-      <c r="X37" s="38"/>
-      <c r="Y37" s="38"/>
+      <c r="X37" s="36"/>
+      <c r="Y37" s="36"/>
       <c r="Z37" s="8" t="s">
         <v>26</v>
       </c>
@@ -3443,15 +3683,15 @@
       <c r="AB37" s="8"/>
     </row>
     <row r="38" spans="1:28">
-      <c r="A38" s="80"/>
-      <c r="B38" s="83"/>
+      <c r="A38" s="88"/>
+      <c r="B38" s="61"/>
       <c r="C38" s="8">
         <v>3</v>
       </c>
-      <c r="D38" s="88"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
@@ -3462,28 +3702,28 @@
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
-      <c r="R38" s="38"/>
-      <c r="S38" s="38"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="38"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
-      <c r="X38" s="38"/>
-      <c r="Y38" s="38"/>
+      <c r="X38" s="36"/>
+      <c r="Y38" s="36"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
     </row>
     <row r="39" spans="1:28" ht="15" thickBot="1">
-      <c r="A39" s="81"/>
-      <c r="B39" s="84"/>
+      <c r="A39" s="89"/>
+      <c r="B39" s="62"/>
       <c r="C39" s="12">
         <v>4</v>
       </c>
-      <c r="D39" s="89"/>
-      <c r="E39" s="90"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="62"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
@@ -3494,96 +3734,96 @@
       <c r="O39" s="12"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
-      <c r="R39" s="38"/>
-      <c r="S39" s="38"/>
-      <c r="T39" s="38"/>
-      <c r="U39" s="38"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
-      <c r="X39" s="38"/>
-      <c r="Y39" s="38"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
     </row>
     <row r="40" spans="1:28" ht="15" thickBot="1"/>
     <row r="41" spans="1:28" ht="20.25" customHeight="1">
-      <c r="A41" s="63" t="s">
+      <c r="A41" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="59" t="s">
+      <c r="C41" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D41" s="59" t="s">
+      <c r="D41" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="59"/>
-      <c r="F41" s="67" t="s">
+      <c r="E41" s="39"/>
+      <c r="F41" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="G41" s="67" t="s">
+      <c r="G41" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H41" s="67" t="s">
+      <c r="H41" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="I41" s="59" t="s">
+      <c r="I41" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="J41" s="59"/>
-      <c r="K41" s="59"/>
-      <c r="L41" s="59" t="s">
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="M41" s="59"/>
-      <c r="N41" s="59"/>
-      <c r="O41" s="59"/>
-      <c r="P41" s="59"/>
-      <c r="Q41" s="77" t="s">
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="R41" s="59" t="s">
+      <c r="R41" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="S41" s="59"/>
-      <c r="T41" s="59"/>
-      <c r="U41" s="59"/>
-      <c r="V41" s="43" t="s">
+      <c r="S41" s="39"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="39"/>
+      <c r="V41" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="W41" s="43" t="s">
+      <c r="W41" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="X41" s="39" t="s">
+      <c r="X41" s="44" t="s">
         <v>49</v>
       </c>
       <c r="Y41" s="40"/>
       <c r="Z41" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AA41" s="43" t="s">
+      <c r="AA41" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="AB41" s="45" t="s">
+      <c r="AB41" s="46" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="26" customHeight="1">
-      <c r="A42" s="64"/>
-      <c r="B42" s="66"/>
-      <c r="C42" s="66"/>
+      <c r="A42" s="73"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
       <c r="D42" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
       <c r="I42" s="7" t="s">
         <v>10</v>
       </c>
@@ -3608,32 +3848,32 @@
       <c r="P42" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="78"/>
-      <c r="R42" s="55" t="s">
+      <c r="Q42" s="86"/>
+      <c r="R42" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="56"/>
-      <c r="T42" s="57" t="s">
+      <c r="S42" s="49"/>
+      <c r="T42" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="U42" s="58"/>
-      <c r="V42" s="62"/>
-      <c r="W42" s="62"/>
-      <c r="X42" s="60"/>
-      <c r="Y42" s="61"/>
-      <c r="Z42" s="61"/>
-      <c r="AA42" s="62"/>
-      <c r="AB42" s="54"/>
+      <c r="U42" s="51"/>
+      <c r="V42" s="43"/>
+      <c r="W42" s="43"/>
+      <c r="X42" s="45"/>
+      <c r="Y42" s="41"/>
+      <c r="Z42" s="41"/>
+      <c r="AA42" s="43"/>
+      <c r="AB42" s="47"/>
     </row>
     <row r="43" spans="1:28">
-      <c r="A43" s="64"/>
-      <c r="B43" s="82" t="s">
+      <c r="A43" s="73"/>
+      <c r="B43" s="60" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="8">
         <v>1</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="36" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="8">
@@ -3675,22 +3915,22 @@
       <c r="Q43" s="9">
         <v>50</v>
       </c>
-      <c r="R43" s="38">
+      <c r="R43" s="36">
         <v>0</v>
       </c>
-      <c r="S43" s="38"/>
-      <c r="T43" s="38">
+      <c r="S43" s="36"/>
+      <c r="T43" s="36">
         <v>0</v>
       </c>
-      <c r="U43" s="38"/>
+      <c r="U43" s="36"/>
       <c r="V43" s="8">
         <v>5</v>
       </c>
       <c r="W43" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="37"/>
+      <c r="X43" s="70"/>
+      <c r="Y43" s="71"/>
       <c r="Z43" s="8" t="s">
         <v>26</v>
       </c>
@@ -3700,12 +3940,12 @@
       <c r="AB43" s="14"/>
     </row>
     <row r="44" spans="1:28">
-      <c r="A44" s="64"/>
-      <c r="B44" s="83"/>
+      <c r="A44" s="73"/>
+      <c r="B44" s="61"/>
       <c r="C44" s="8">
         <v>2</v>
       </c>
-      <c r="D44" s="38"/>
+      <c r="D44" s="36"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
@@ -3739,22 +3979,22 @@
       <c r="Q44" s="9">
         <v>130</v>
       </c>
-      <c r="R44" s="38">
+      <c r="R44" s="36">
         <v>0</v>
       </c>
-      <c r="S44" s="38"/>
-      <c r="T44" s="38">
+      <c r="S44" s="36"/>
+      <c r="T44" s="36">
         <v>0</v>
       </c>
-      <c r="U44" s="38"/>
+      <c r="U44" s="36"/>
       <c r="V44" s="8">
         <v>5</v>
       </c>
       <c r="W44" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X44" s="36"/>
-      <c r="Y44" s="37"/>
+      <c r="X44" s="70"/>
+      <c r="Y44" s="71"/>
       <c r="Z44" s="8" t="s">
         <v>26</v>
       </c>
@@ -3764,12 +4004,12 @@
       <c r="AB44" s="14"/>
     </row>
     <row r="45" spans="1:28">
-      <c r="A45" s="64"/>
-      <c r="B45" s="83"/>
+      <c r="A45" s="73"/>
+      <c r="B45" s="61"/>
       <c r="C45" s="8">
         <v>3</v>
       </c>
-      <c r="D45" s="38"/>
+      <c r="D45" s="36"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
@@ -3783,25 +4023,25 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-      <c r="R45" s="38"/>
-      <c r="S45" s="38"/>
-      <c r="T45" s="38"/>
-      <c r="U45" s="38"/>
+      <c r="R45" s="36"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+      <c r="U45" s="36"/>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
-      <c r="X45" s="36"/>
-      <c r="Y45" s="37"/>
+      <c r="X45" s="70"/>
+      <c r="Y45" s="71"/>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="14"/>
     </row>
     <row r="46" spans="1:28">
-      <c r="A46" s="64"/>
-      <c r="B46" s="83"/>
+      <c r="A46" s="73"/>
+      <c r="B46" s="61"/>
       <c r="C46" s="8">
         <v>4</v>
       </c>
-      <c r="D46" s="38"/>
+      <c r="D46" s="36"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
@@ -3815,28 +4055,28 @@
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
       <c r="Q46" s="9"/>
-      <c r="R46" s="38"/>
-      <c r="S46" s="38"/>
-      <c r="T46" s="38"/>
-      <c r="U46" s="38"/>
+      <c r="R46" s="36"/>
+      <c r="S46" s="36"/>
+      <c r="T46" s="36"/>
+      <c r="U46" s="36"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="37"/>
+      <c r="X46" s="70"/>
+      <c r="Y46" s="71"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="14"/>
     </row>
     <row r="47" spans="1:28">
-      <c r="A47" s="64"/>
-      <c r="B47" s="83"/>
+      <c r="A47" s="73"/>
+      <c r="B47" s="61"/>
       <c r="C47" s="8">
         <v>1</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="71"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="68"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -3847,28 +4087,28 @@
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
       <c r="Q47" s="11"/>
-      <c r="R47" s="38"/>
-      <c r="S47" s="38"/>
-      <c r="T47" s="38"/>
-      <c r="U47" s="38"/>
+      <c r="R47" s="36"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+      <c r="U47" s="36"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
-      <c r="X47" s="36"/>
-      <c r="Y47" s="37"/>
+      <c r="X47" s="70"/>
+      <c r="Y47" s="71"/>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="14"/>
     </row>
     <row r="48" spans="1:28">
-      <c r="A48" s="64"/>
-      <c r="B48" s="83"/>
+      <c r="A48" s="73"/>
+      <c r="B48" s="61"/>
       <c r="C48" s="8">
         <v>2</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
@@ -3879,28 +4119,28 @@
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
       <c r="Q48" s="9"/>
-      <c r="R48" s="38"/>
-      <c r="S48" s="38"/>
-      <c r="T48" s="38"/>
-      <c r="U48" s="38"/>
+      <c r="R48" s="36"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+      <c r="U48" s="36"/>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
-      <c r="X48" s="36"/>
-      <c r="Y48" s="37"/>
+      <c r="X48" s="70"/>
+      <c r="Y48" s="71"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="14"/>
     </row>
     <row r="49" spans="1:28">
-      <c r="A49" s="64"/>
-      <c r="B49" s="83"/>
+      <c r="A49" s="73"/>
+      <c r="B49" s="61"/>
       <c r="C49" s="8">
         <v>3</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -3911,28 +4151,28 @@
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
       <c r="Q49" s="9"/>
-      <c r="R49" s="38"/>
-      <c r="S49" s="38"/>
-      <c r="T49" s="38"/>
-      <c r="U49" s="38"/>
+      <c r="R49" s="36"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+      <c r="U49" s="36"/>
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
-      <c r="X49" s="36"/>
-      <c r="Y49" s="37"/>
+      <c r="X49" s="70"/>
+      <c r="Y49" s="71"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="15"/>
       <c r="AB49" s="14"/>
     </row>
     <row r="50" spans="1:28" ht="15" thickBot="1">
-      <c r="A50" s="65"/>
-      <c r="B50" s="84"/>
+      <c r="A50" s="82"/>
+      <c r="B50" s="62"/>
       <c r="C50" s="12">
         <v>4</v>
       </c>
-      <c r="D50" s="70"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
@@ -3943,14 +4183,14 @@
       <c r="O50" s="12"/>
       <c r="P50" s="12"/>
       <c r="Q50" s="13"/>
-      <c r="R50" s="51"/>
-      <c r="S50" s="51"/>
-      <c r="T50" s="51"/>
-      <c r="U50" s="51"/>
+      <c r="R50" s="69"/>
+      <c r="S50" s="69"/>
+      <c r="T50" s="69"/>
+      <c r="U50" s="69"/>
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
-      <c r="X50" s="52"/>
-      <c r="Y50" s="53"/>
+      <c r="X50" s="98"/>
+      <c r="Y50" s="99"/>
       <c r="Z50" s="12"/>
       <c r="AA50" s="12"/>
       <c r="AB50" s="16"/>
@@ -3958,125 +4198,125 @@
     <row r="51" spans="1:28" ht="15" thickBot="1"/>
     <row r="52" spans="1:28">
       <c r="A52" s="3"/>
-      <c r="C52" s="99" t="s">
+      <c r="C52" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="100"/>
-      <c r="E52" s="100"/>
-      <c r="F52" s="100"/>
-      <c r="G52" s="100"/>
-      <c r="H52" s="100"/>
-      <c r="I52" s="100"/>
-      <c r="J52" s="100"/>
-      <c r="K52" s="100"/>
-      <c r="L52" s="100"/>
-      <c r="M52" s="100"/>
-      <c r="N52" s="100"/>
-      <c r="O52" s="100"/>
-      <c r="P52" s="100"/>
-      <c r="Q52" s="100"/>
-      <c r="R52" s="100"/>
-      <c r="S52" s="100"/>
-      <c r="T52" s="100"/>
-      <c r="U52" s="100"/>
-      <c r="V52" s="100"/>
-      <c r="W52" s="100"/>
-      <c r="X52" s="101"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="53"/>
+      <c r="M52" s="53"/>
+      <c r="N52" s="53"/>
+      <c r="O52" s="53"/>
+      <c r="P52" s="53"/>
+      <c r="Q52" s="53"/>
+      <c r="R52" s="53"/>
+      <c r="S52" s="53"/>
+      <c r="T52" s="53"/>
+      <c r="U52" s="53"/>
+      <c r="V52" s="53"/>
+      <c r="W52" s="53"/>
+      <c r="X52" s="54"/>
       <c r="Y52" s="3"/>
     </row>
     <row r="53" spans="1:28">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="102"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="27"/>
-      <c r="N53" s="27"/>
-      <c r="O53" s="27"/>
-      <c r="P53" s="27"/>
-      <c r="Q53" s="27"/>
-      <c r="R53" s="27"/>
-      <c r="S53" s="27"/>
-      <c r="T53" s="27"/>
-      <c r="U53" s="27"/>
-      <c r="V53" s="27"/>
-      <c r="W53" s="27"/>
-      <c r="X53" s="103"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+      <c r="R53" s="35"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="35"/>
+      <c r="U53" s="35"/>
+      <c r="V53" s="35"/>
+      <c r="W53" s="35"/>
+      <c r="X53" s="56"/>
       <c r="Y53" s="3"/>
     </row>
     <row r="54" spans="1:28" ht="15" thickBot="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
-      <c r="C54" s="104"/>
-      <c r="D54" s="105"/>
-      <c r="E54" s="105"/>
-      <c r="F54" s="105"/>
-      <c r="G54" s="105"/>
-      <c r="H54" s="105"/>
-      <c r="I54" s="105"/>
-      <c r="J54" s="105"/>
-      <c r="K54" s="105"/>
-      <c r="L54" s="105"/>
-      <c r="M54" s="105"/>
-      <c r="N54" s="105"/>
-      <c r="O54" s="105"/>
-      <c r="P54" s="105"/>
-      <c r="Q54" s="105"/>
-      <c r="R54" s="105"/>
-      <c r="S54" s="105"/>
-      <c r="T54" s="105"/>
-      <c r="U54" s="105"/>
-      <c r="V54" s="105"/>
-      <c r="W54" s="105"/>
-      <c r="X54" s="106"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="58"/>
+      <c r="K54" s="58"/>
+      <c r="L54" s="58"/>
+      <c r="M54" s="58"/>
+      <c r="N54" s="58"/>
+      <c r="O54" s="58"/>
+      <c r="P54" s="58"/>
+      <c r="Q54" s="58"/>
+      <c r="R54" s="58"/>
+      <c r="S54" s="58"/>
+      <c r="T54" s="58"/>
+      <c r="U54" s="58"/>
+      <c r="V54" s="58"/>
+      <c r="W54" s="58"/>
+      <c r="X54" s="59"/>
       <c r="Y54" s="3"/>
     </row>
     <row r="55" spans="1:28" ht="15" thickBot="1"/>
     <row r="56" spans="1:28" ht="23" customHeight="1">
-      <c r="A56" s="63" t="s">
+      <c r="A56" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="B56" s="92" t="s">
+      <c r="B56" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="92"/>
-      <c r="D56" s="92"/>
-      <c r="E56" s="95"/>
-      <c r="F56" s="95"/>
-      <c r="G56" s="95"/>
-      <c r="H56" s="95"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="95"/>
-      <c r="K56" s="95"/>
-      <c r="L56" s="95"/>
-      <c r="M56" s="95"/>
-      <c r="N56" s="95"/>
-      <c r="O56" s="95"/>
-      <c r="P56" s="95"/>
-      <c r="Q56" s="95"/>
-      <c r="R56" s="95"/>
-      <c r="S56" s="95"/>
-      <c r="T56" s="95"/>
-      <c r="U56" s="95"/>
-      <c r="V56" s="95"/>
-      <c r="W56" s="95"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="77"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="77"/>
+      <c r="I56" s="77"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="77"/>
+      <c r="L56" s="77"/>
+      <c r="M56" s="77"/>
+      <c r="N56" s="77"/>
+      <c r="O56" s="77"/>
+      <c r="P56" s="77"/>
+      <c r="Q56" s="77"/>
+      <c r="R56" s="77"/>
+      <c r="S56" s="77"/>
+      <c r="T56" s="77"/>
+      <c r="U56" s="77"/>
+      <c r="V56" s="77"/>
+      <c r="W56" s="77"/>
       <c r="X56" s="4"/>
       <c r="Y56" s="5"/>
     </row>
     <row r="57" spans="1:28" ht="24" customHeight="1">
-      <c r="A57" s="64"/>
-      <c r="B57" s="93" t="s">
+      <c r="A57" s="73"/>
+      <c r="B57" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="93"/>
-      <c r="D57" s="93"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
       <c r="E57" s="26"/>
       <c r="F57" s="26"/>
       <c r="G57" s="26"/>
@@ -4097,15 +4337,15 @@
       <c r="V57" s="26"/>
       <c r="W57" s="26"/>
       <c r="X57" s="26"/>
-      <c r="Y57" s="96"/>
+      <c r="Y57" s="78"/>
     </row>
     <row r="58" spans="1:28" ht="26" customHeight="1">
-      <c r="A58" s="64"/>
-      <c r="B58" s="93" t="s">
+      <c r="A58" s="73"/>
+      <c r="B58" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="75"/>
       <c r="E58" s="26"/>
       <c r="F58" s="26"/>
       <c r="G58" s="26"/>
@@ -4126,15 +4366,15 @@
       <c r="V58" s="26"/>
       <c r="W58" s="26"/>
       <c r="X58" s="26"/>
-      <c r="Y58" s="96"/>
+      <c r="Y58" s="78"/>
     </row>
     <row r="59" spans="1:28" ht="23" customHeight="1">
-      <c r="A59" s="64"/>
-      <c r="B59" s="93" t="s">
+      <c r="A59" s="73"/>
+      <c r="B59" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="93"/>
-      <c r="D59" s="93"/>
+      <c r="C59" s="75"/>
+      <c r="D59" s="75"/>
       <c r="E59" s="26"/>
       <c r="F59" s="26"/>
       <c r="G59" s="26"/>
@@ -4155,13 +4395,13 @@
       <c r="V59" s="26"/>
       <c r="W59" s="26"/>
       <c r="X59" s="26"/>
-      <c r="Y59" s="96"/>
+      <c r="Y59" s="78"/>
     </row>
     <row r="60" spans="1:28" ht="26" customHeight="1" thickBot="1">
-      <c r="A60" s="64"/>
-      <c r="B60" s="94"/>
-      <c r="C60" s="94"/>
-      <c r="D60" s="94"/>
+      <c r="A60" s="73"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -4185,79 +4425,181 @@
       <c r="Y60" s="2"/>
     </row>
     <row r="69" spans="2:25">
-      <c r="B69" s="97" t="s">
+      <c r="B69" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="98"/>
-      <c r="D69" s="98"/>
-      <c r="E69" s="98"/>
-      <c r="F69" s="98"/>
-      <c r="G69" s="98"/>
-      <c r="H69" s="98"/>
-      <c r="I69" s="98"/>
-      <c r="J69" s="98"/>
-      <c r="K69" s="98"/>
-      <c r="L69" s="98"/>
-      <c r="M69" s="98"/>
-      <c r="N69" s="98"/>
-      <c r="O69" s="98"/>
-      <c r="P69" s="98"/>
-      <c r="Q69" s="98"/>
-      <c r="R69" s="98"/>
-      <c r="S69" s="98"/>
-      <c r="T69" s="98"/>
-      <c r="U69" s="98"/>
-      <c r="V69" s="98"/>
-      <c r="W69" s="98"/>
-      <c r="X69" s="98"/>
-      <c r="Y69" s="98"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="38"/>
+      <c r="L69" s="38"/>
+      <c r="M69" s="38"/>
+      <c r="N69" s="38"/>
+      <c r="O69" s="38"/>
+      <c r="P69" s="38"/>
+      <c r="Q69" s="38"/>
+      <c r="R69" s="38"/>
+      <c r="S69" s="38"/>
+      <c r="T69" s="38"/>
+      <c r="U69" s="38"/>
+      <c r="V69" s="38"/>
+      <c r="W69" s="38"/>
+      <c r="X69" s="38"/>
+      <c r="Y69" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="223">
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="B69:Y69"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C52:X54"/>
-    <mergeCell ref="B43:B50"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D47:D50"/>
-    <mergeCell ref="E47:E50"/>
-    <mergeCell ref="F47:F50"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E56:W56"/>
-    <mergeCell ref="E57:Y57"/>
-    <mergeCell ref="E58:Y58"/>
-    <mergeCell ref="E59:Y59"/>
-    <mergeCell ref="V26:V27"/>
-    <mergeCell ref="W26:W27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:P26"/>
-    <mergeCell ref="G47:G50"/>
-    <mergeCell ref="V41:V42"/>
-    <mergeCell ref="W41:W42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="X37:Y37"/>
+    <mergeCell ref="X38:Y38"/>
+    <mergeCell ref="X39:Y39"/>
+    <mergeCell ref="X26:Y27"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AB26:AB27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="T47:U47"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="X48:Y48"/>
+    <mergeCell ref="X49:Y49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="AB41:AB42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="X43:Y43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="R41:U41"/>
+    <mergeCell ref="X41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="R26:U26"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="X15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="A15:A24"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:P4"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="D32:D39"/>
+    <mergeCell ref="E32:E39"/>
+    <mergeCell ref="F28:F39"/>
+    <mergeCell ref="G32:G39"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="Q15:Q16"/>
     <mergeCell ref="T10:U10"/>
     <mergeCell ref="T11:U11"/>
     <mergeCell ref="R45:S45"/>
@@ -4282,142 +4624,16 @@
     <mergeCell ref="Q41:Q42"/>
     <mergeCell ref="A26:A39"/>
     <mergeCell ref="B6:B13"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="G28:G31"/>
-    <mergeCell ref="D32:D39"/>
-    <mergeCell ref="E32:E39"/>
-    <mergeCell ref="F28:F39"/>
-    <mergeCell ref="G32:G39"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A4:A13"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:P4"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="A15:A24"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="AB15:AB16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="X15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="R41:U41"/>
-    <mergeCell ref="X41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="R26:U26"/>
-    <mergeCell ref="AB41:AB42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="X43:Y43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="T47:U47"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="X49:Y49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="X50:Y50"/>
-    <mergeCell ref="X26:Y27"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AB26:AB27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="W26:W27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:P26"/>
+    <mergeCell ref="G47:G50"/>
+    <mergeCell ref="V41:V42"/>
+    <mergeCell ref="W41:W42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
     <mergeCell ref="T31:U31"/>
     <mergeCell ref="T32:U32"/>
     <mergeCell ref="T33:U33"/>
@@ -4427,16 +4643,40 @@
     <mergeCell ref="T37:U37"/>
     <mergeCell ref="T38:U38"/>
     <mergeCell ref="T39:U39"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="X34:Y34"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="X37:Y37"/>
-    <mergeCell ref="X38:Y38"/>
-    <mergeCell ref="X39:Y39"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E56:W56"/>
+    <mergeCell ref="E57:Y57"/>
+    <mergeCell ref="E58:Y58"/>
+    <mergeCell ref="E59:Y59"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="B69:Y69"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C52:X54"/>
+    <mergeCell ref="B43:B50"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D47:D50"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="F47:F50"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="V26:V27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="5">
@@ -4484,47 +4724,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.5" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="31" t="s">
         <v>67</v>
       </c>
       <c r="B3" s="26"/>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10">
@@ -4547,7 +4787,7 @@
         <v>81</v>
       </c>
       <c r="I4" s="20"/>
-      <c r="J4" s="35"/>
+      <c r="J4" s="32"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="26"/>
@@ -4571,7 +4811,7 @@
         <v>77</v>
       </c>
       <c r="I5" s="22"/>
-      <c r="J5" s="35"/>
+      <c r="J5" s="32"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="26"/>
@@ -4595,7 +4835,7 @@
         <v>78</v>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="35"/>
+      <c r="J6" s="32"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="26"/>
@@ -4619,7 +4859,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="22"/>
-      <c r="J7" s="35"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="26"/>
@@ -4643,7 +4883,7 @@
         <v>84</v>
       </c>
       <c r="I8" s="22"/>
-      <c r="J8" s="35"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="26"/>
@@ -4667,7 +4907,7 @@
         <v>85</v>
       </c>
       <c r="I9" s="22"/>
-      <c r="J9" s="35"/>
+      <c r="J9" s="32"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="26"/>
@@ -4691,21 +4931,21 @@
         <v>86</v>
       </c>
       <c r="I10" s="22"/>
-      <c r="J10" s="35"/>
+      <c r="J10" s="32"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="26"/>
       <c r="B11" s="26"/>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="35"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="26"/>
@@ -4727,7 +4967,7 @@
         <v>81</v>
       </c>
       <c r="I12" s="20"/>
-      <c r="J12" s="35"/>
+      <c r="J12" s="32"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="26"/>
@@ -4751,7 +4991,7 @@
         <v>77</v>
       </c>
       <c r="I13" s="22"/>
-      <c r="J13" s="35"/>
+      <c r="J13" s="32"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="26"/>
@@ -4775,7 +5015,7 @@
         <v>79</v>
       </c>
       <c r="I14" s="22"/>
-      <c r="J14" s="35"/>
+      <c r="J14" s="32"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="26"/>
@@ -4799,7 +5039,7 @@
         <v>4</v>
       </c>
       <c r="I15" s="22"/>
-      <c r="J15" s="35"/>
+      <c r="J15" s="32"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="26"/>
@@ -4823,7 +5063,7 @@
         <v>84</v>
       </c>
       <c r="I16" s="22"/>
-      <c r="J16" s="35"/>
+      <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="26"/>
@@ -4847,7 +5087,7 @@
         <v>85</v>
       </c>
       <c r="I17" s="22"/>
-      <c r="J17" s="35"/>
+      <c r="J17" s="32"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="26"/>
@@ -4871,21 +5111,21 @@
         <v>86</v>
       </c>
       <c r="I18" s="22"/>
-      <c r="J18" s="35"/>
+      <c r="J18" s="32"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="26"/>
       <c r="B19" s="26"/>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="35"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="32"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="26"/>
@@ -4907,7 +5147,7 @@
         <v>81</v>
       </c>
       <c r="I20" s="20"/>
-      <c r="J20" s="35"/>
+      <c r="J20" s="32"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="26"/>
@@ -4931,7 +5171,7 @@
         <v>56</v>
       </c>
       <c r="I21" s="22"/>
-      <c r="J21" s="35"/>
+      <c r="J21" s="32"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="26"/>
@@ -4955,7 +5195,7 @@
         <v>19</v>
       </c>
       <c r="I22" s="22"/>
-      <c r="J22" s="35"/>
+      <c r="J22" s="32"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="26"/>
@@ -4979,7 +5219,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="22"/>
-      <c r="J23" s="35"/>
+      <c r="J23" s="32"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="26"/>
@@ -4988,10 +5228,10 @@
         <v>73</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>84</v>
@@ -5003,7 +5243,7 @@
         <v>84</v>
       </c>
       <c r="I24" s="22"/>
-      <c r="J24" s="35"/>
+      <c r="J24" s="32"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="26"/>
@@ -5027,7 +5267,7 @@
         <v>85</v>
       </c>
       <c r="I25" s="22"/>
-      <c r="J25" s="35"/>
+      <c r="J25" s="32"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="26"/>
@@ -5051,21 +5291,21 @@
         <v>86</v>
       </c>
       <c r="I26" s="22"/>
-      <c r="J26" s="35"/>
+      <c r="J26" s="32"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="26"/>
       <c r="B27" s="26"/>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="35"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="26"/>
@@ -5087,7 +5327,7 @@
         <v>81</v>
       </c>
       <c r="I28" s="20"/>
-      <c r="J28" s="35"/>
+      <c r="J28" s="32"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="26"/>
@@ -5105,7 +5345,7 @@
         <v>78</v>
       </c>
       <c r="I29" s="22"/>
-      <c r="J29" s="35"/>
+      <c r="J29" s="32"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="26"/>
@@ -5123,7 +5363,7 @@
         <v>59</v>
       </c>
       <c r="I30" s="22"/>
-      <c r="J30" s="35"/>
+      <c r="J30" s="32"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="26"/>
@@ -5141,7 +5381,7 @@
         <v>8</v>
       </c>
       <c r="I31" s="22"/>
-      <c r="J31" s="35"/>
+      <c r="J31" s="32"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="26"/>
@@ -5159,7 +5399,7 @@
         <v>84</v>
       </c>
       <c r="I32" s="22"/>
-      <c r="J32" s="35"/>
+      <c r="J32" s="32"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="26"/>
@@ -5177,7 +5417,7 @@
         <v>85</v>
       </c>
       <c r="I33" s="22"/>
-      <c r="J33" s="35"/>
+      <c r="J33" s="32"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="26"/>
@@ -5195,33 +5435,33 @@
         <v>86</v>
       </c>
       <c r="I34" s="22"/>
-      <c r="J34" s="35"/>
+      <c r="J34" s="32"/>
     </row>
     <row r="35" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="30"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="19" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D35" s="22">
         <v>32</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>95</v>
+      <c r="E35" s="19" t="s">
+        <v>114</v>
       </c>
       <c r="F35" s="22">
         <v>22</v>
       </c>
-      <c r="G35" s="22" t="s">
-        <v>96</v>
+      <c r="G35" s="19" t="s">
+        <v>115</v>
       </c>
       <c r="H35" s="22">
         <v>22</v>
       </c>
-      <c r="I35" s="22" t="s">
-        <v>97</v>
+      <c r="I35" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="J35" s="22" t="s">
         <v>84</v>
@@ -5229,47 +5469,47 @@
     </row>
     <row r="36" spans="1:10" ht="34.75" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="19" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D36" s="22">
         <v>2</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>95</v>
+      <c r="E36" s="19" t="s">
+        <v>114</v>
       </c>
       <c r="F36" s="22">
         <v>2</v>
       </c>
-      <c r="G36" s="22" t="s">
-        <v>96</v>
+      <c r="G36" s="19" t="s">
+        <v>115</v>
       </c>
       <c r="H36" s="22">
         <v>2</v>
       </c>
-      <c r="I36" s="22" t="s">
-        <v>97</v>
+      <c r="I36" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="J36" s="22" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
+      <c r="A37" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
     </row>
     <row r="38" spans="1:10" ht="26" customHeight="1">
       <c r="A38" s="22"/>
@@ -5344,14 +5584,19 @@
       <c r="J43" s="26"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="F42:J42"/>
+    <mergeCell ref="F43:J43"/>
+    <mergeCell ref="F44:J44"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -5365,11 +5610,6 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="F42:J42"/>
-    <mergeCell ref="F43:J43"/>
-    <mergeCell ref="F44:J44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5384,9 +5624,369 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" style="108" customWidth="1"/>
+    <col min="2" max="2" width="6.5" style="108" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="108" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="108" customWidth="1"/>
+    <col min="5" max="5" width="15" style="108" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" style="108" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="108" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" style="108" customWidth="1"/>
+    <col min="9" max="9" width="16" style="108" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" style="108" customWidth="1"/>
+    <col min="11" max="11" width="3.6640625" style="108" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="108"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="43.5" customHeight="1">
+      <c r="A1" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+    </row>
+    <row r="2" spans="1:10" ht="20" customHeight="1">
+      <c r="A2" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" spans="1:10" ht="29" customHeight="1">
+      <c r="A3" s="110"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="111" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="111" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1">
+      <c r="A4" s="112" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="21">
+        <v>71</v>
+      </c>
+      <c r="E4" s="21">
+        <v>40</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+    </row>
+    <row r="5" spans="1:10" ht="28" customHeight="1">
+      <c r="A5" s="112" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1">
+      <c r="A6" s="112" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="112"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1">
+      <c r="A7" s="112" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="112"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1">
+      <c r="A8" s="112" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="110"/>
+    </row>
+    <row r="9" spans="1:10" ht="32" customHeight="1">
+      <c r="A9" s="112" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="110"/>
+    </row>
+    <row r="10" spans="1:10" ht="31" customHeight="1">
+      <c r="A10" s="114" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="114"/>
+      <c r="C10" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="113">
+        <v>43</v>
+      </c>
+      <c r="E10" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="113">
+        <v>43</v>
+      </c>
+      <c r="G10" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="113">
+        <v>43</v>
+      </c>
+      <c r="I10" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10" s="113" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="33" customHeight="1">
+      <c r="A11" s="110" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="110"/>
+      <c r="C11" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="113">
+        <v>7</v>
+      </c>
+      <c r="E11" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="113">
+        <v>7</v>
+      </c>
+      <c r="G11" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" s="113">
+        <v>7</v>
+      </c>
+      <c r="I11" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="113" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="20" customHeight="1">
+      <c r="A12" s="116" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+    </row>
+    <row r="13" spans="1:10" ht="24" customHeight="1">
+      <c r="A13" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="117"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="115" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="110" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="113"/>
+    </row>
+    <row r="14" spans="1:10" ht="32" customHeight="1">
+      <c r="A14" s="117"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="115" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="113"/>
+    </row>
+    <row r="15" spans="1:10" ht="31" customHeight="1">
+      <c r="A15" s="118"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="113"/>
+    </row>
+    <row r="16" spans="1:10" ht="26" customHeight="1">
+      <c r="A16" s="118"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+    </row>
+    <row r="17" spans="1:10" ht="29" customHeight="1">
+      <c r="A17" s="118"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+    </row>
+    <row r="18" spans="1:10" ht="19" customHeight="1">
+      <c r="A18" s="118"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
+    </row>
+    <row r="19" spans="1:10" ht="19" customHeight="1">
+      <c r="A19" s="118"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+    </row>
+    <row r="20" spans="1:10" ht="200.25" customHeight="1">
+      <c r="A20" s="107"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A13:C14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="H3:J9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5396,4 +5996,284 @@
   </headerFooter>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6720E6-AB1B-3348-8616-F64CCABFF6B1}">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="29.1640625" style="108" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" style="108" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="108" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" style="108" customWidth="1"/>
+    <col min="5" max="5" width="26" style="108" customWidth="1"/>
+    <col min="6" max="6" width="27.5" style="108" customWidth="1"/>
+    <col min="7" max="7" width="27.1640625" style="108" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" style="108" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="108" customWidth="1"/>
+    <col min="10" max="10" width="27" style="108" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" style="108" customWidth="1"/>
+    <col min="12" max="12" width="27.1640625" style="108" customWidth="1"/>
+    <col min="13" max="13" width="25.1640625" style="108" customWidth="1"/>
+    <col min="14" max="14" width="27.33203125" style="108" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="108"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="43.5" customHeight="1">
+      <c r="A1" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+    </row>
+    <row r="2" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A2" s="120" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+    </row>
+    <row r="3" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A3" s="119" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="121" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="121" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="121" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="121" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="I3" s="121" t="s">
+        <v>135</v>
+      </c>
+      <c r="J3" s="121" t="s">
+        <v>136</v>
+      </c>
+      <c r="K3" s="121" t="s">
+        <v>137</v>
+      </c>
+      <c r="L3" s="123" t="s">
+        <v>118</v>
+      </c>
+      <c r="M3" s="124" t="s">
+        <v>144</v>
+      </c>
+      <c r="N3" s="123"/>
+    </row>
+    <row r="4" spans="1:14" ht="26" customHeight="1">
+      <c r="A4" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+    </row>
+    <row r="5" spans="1:14" ht="26" customHeight="1">
+      <c r="A5" s="119" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="J5" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="122" t="s">
+        <v>145</v>
+      </c>
+      <c r="M5" s="125">
+        <v>8</v>
+      </c>
+      <c r="N5" s="125"/>
+    </row>
+    <row r="6" spans="1:14" ht="26" customHeight="1">
+      <c r="A6" s="119" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="122" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6" s="122" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="122" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="122" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="122" t="s">
+        <v>143</v>
+      </c>
+      <c r="J6" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="122" t="s">
+        <v>145</v>
+      </c>
+      <c r="M6" s="125">
+        <v>8</v>
+      </c>
+      <c r="N6" s="125"/>
+    </row>
+    <row r="7" spans="1:14" ht="26" customHeight="1">
+      <c r="A7" s="115" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="113"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="113"/>
+      <c r="N7" s="113"/>
+    </row>
+    <row r="8" spans="1:14" ht="26" customHeight="1">
+      <c r="A8" s="118" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="118"/>
+    </row>
+    <row r="9" spans="1:14" ht="28.5" customHeight="1"/>
+    <row r="10" spans="1:14" ht="25" customHeight="1"/>
+    <row r="11" spans="1:14" ht="25" customHeight="1"/>
+    <row r="12" spans="1:14" ht="25" customHeight="1"/>
+    <row r="13" spans="1:14" ht="25" customHeight="1"/>
+    <row r="14" spans="1:14" ht="25" customHeight="1"/>
+    <row r="15" spans="1:14" ht="25" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>